--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D4B15-BCD2-47A9-A2A5-0C3DBF508F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976F0B02-42E2-4EFB-B10B-AC1DAB7B8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="3" r:id="rId1"/>
@@ -2023,73 +2023,74 @@
   <dimension ref="A1:A113"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="18">
+    <row r="1" spans="1:1" ht="18" hidden="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" hidden="1">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" hidden="1">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" hidden="1">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" hidden="1">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" hidden="1">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" hidden="1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" hidden="1">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" hidden="1">
       <c r="A9" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" hidden="1">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" hidden="1">
       <c r="A11" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" hidden="1">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" hidden="1">
       <c r="A13" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" hidden="1">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" hidden="1">
       <c r="A15" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" hidden="1">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" hidden="1">
       <c r="A17" s="7" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="18" spans="1:1" hidden="1"/>
     <row r="19" spans="1:1" ht="18">
       <c r="A19" s="6" t="s">
         <v>8</v>
@@ -2210,74 +2211,75 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="18">
+    <row r="53" spans="1:1" ht="18" hidden="1">
       <c r="A53" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="54" spans="1:1" hidden="1"/>
+    <row r="55" spans="1:1" hidden="1">
       <c r="A55" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" hidden="1">
       <c r="A56" s="4"/>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" hidden="1">
       <c r="A57" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" hidden="1">
       <c r="A58" s="4"/>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" hidden="1">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" hidden="1">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" hidden="1">
       <c r="A61" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" hidden="1">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" hidden="1">
       <c r="A63" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" hidden="1">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" hidden="1">
       <c r="A65" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" hidden="1">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" hidden="1">
       <c r="A67" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" hidden="1">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" hidden="1">
       <c r="A69" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" hidden="1">
       <c r="A70" s="4"/>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" hidden="1">
       <c r="A71" s="7" t="s">
         <v>31</v>
       </c>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976F0B02-42E2-4EFB-B10B-AC1DAB7B8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A187C1-CAE6-457F-8C5F-9611214D802E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2020,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD60BB66-895D-4009-B2A1-9C303AD5B319}">
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:A114"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1" ht="18" hidden="1">
@@ -2120,313 +2120,318 @@
     <row r="26" spans="1:1">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:1" hidden="1">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:1" hidden="1">
+      <c r="A28" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="18">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:1" hidden="1"/>
+    <row r="30" spans="1:1" ht="18">
+      <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="4"/>
-    </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="4"/>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="4"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="5"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="5"/>
-    </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="5"/>
-    </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="4"/>
-    </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="4"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="4"/>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="4"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="5"/>
+      <c r="A46" s="4"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="5"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="5"/>
-    </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="5"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="4"/>
-    </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="4"/>
+    </row>
+    <row r="52" spans="1:1" hidden="1">
+      <c r="A52" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="18" hidden="1">
-      <c r="A53" s="6" t="s">
+    <row r="54" spans="1:1" ht="18" hidden="1">
+      <c r="A54" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:1" hidden="1"/>
-    <row r="55" spans="1:1" hidden="1">
-      <c r="A55" t="s">
+    <row r="55" spans="1:1" hidden="1"/>
+    <row r="56" spans="1:1" hidden="1">
+      <c r="A56" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:1" hidden="1">
-      <c r="A56" s="4"/>
-    </row>
     <row r="57" spans="1:1" hidden="1">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" spans="1:1" hidden="1">
+      <c r="A58" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" hidden="1">
-      <c r="A58" s="4"/>
     </row>
     <row r="59" spans="1:1" hidden="1">
       <c r="A59" s="4"/>
     </row>
     <row r="60" spans="1:1" hidden="1">
-      <c r="A60" s="5"/>
+      <c r="A60" s="4"/>
     </row>
     <row r="61" spans="1:1" hidden="1">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="5"/>
+    </row>
+    <row r="62" spans="1:1" hidden="1">
+      <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:1" hidden="1">
-      <c r="A62" s="5"/>
-    </row>
     <row r="63" spans="1:1" hidden="1">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="5"/>
+    </row>
+    <row r="64" spans="1:1" hidden="1">
+      <c r="A64" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:1" hidden="1">
-      <c r="A64" s="5"/>
-    </row>
     <row r="65" spans="1:1" hidden="1">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="5"/>
+    </row>
+    <row r="66" spans="1:1" hidden="1">
+      <c r="A66" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1">
-      <c r="A66" s="5"/>
-    </row>
     <row r="67" spans="1:1" hidden="1">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="5"/>
+    </row>
+    <row r="68" spans="1:1" hidden="1">
+      <c r="A68" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1">
-      <c r="A68" s="4"/>
-    </row>
     <row r="69" spans="1:1" hidden="1">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="4"/>
+    </row>
+    <row r="70" spans="1:1" hidden="1">
+      <c r="A70" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1">
-      <c r="A70" s="4"/>
-    </row>
     <row r="71" spans="1:1" hidden="1">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="4"/>
+    </row>
+    <row r="72" spans="1:1" hidden="1">
+      <c r="A72" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="18">
-      <c r="A73" s="6" t="s">
+    <row r="74" spans="1:1" ht="18" hidden="1">
+      <c r="A74" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:1" hidden="1">
+      <c r="A75" s="4"/>
+    </row>
+    <row r="76" spans="1:1" hidden="1">
+      <c r="A76" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="7" t="s">
+    <row r="77" spans="1:1" hidden="1">
+      <c r="A77" s="4"/>
+    </row>
+    <row r="78" spans="1:1" hidden="1">
+      <c r="A78" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="18">
-      <c r="A79" s="6" t="s">
+    <row r="79" spans="1:1" hidden="1"/>
+    <row r="80" spans="1:1" ht="18">
+      <c r="A80" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="4"/>
-    </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="4"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="4"/>
-    </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="4"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="18">
-      <c r="A85" s="6" t="s">
+    <row r="86" spans="1:1" ht="18">
+      <c r="A86" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="4"/>
-    </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="4"/>
-    </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="4"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="4"/>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="4"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="5"/>
+      <c r="A94" s="4"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="5"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="5"/>
-    </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="5"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="5"/>
-    </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="5"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="4"/>
-    </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="4"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="4"/>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="4"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="5"/>
+      <c r="A104" s="4"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="5"/>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="18">
-      <c r="A107" s="6" t="s">
+    <row r="108" spans="1:1" ht="18">
+      <c r="A108" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="4"/>
-    </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="4"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="4"/>
-    </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="4"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4" t="s">
         <v>50</v>
       </c>
     </row>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A187C1-CAE6-457F-8C5F-9611214D802E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E87CAA-9191-4A65-9AD2-FEE635874F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Todo" sheetId="3" r:id="rId1"/>
-    <sheet name="Classes" sheetId="4" r:id="rId2"/>
+    <sheet name="New Todo" sheetId="5" r:id="rId1"/>
+    <sheet name="Todo" sheetId="3" r:id="rId2"/>
+    <sheet name="Classes" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>2. Scene Architecture (The "GameController")</t>
   </si>
@@ -1627,13 +1628,177 @@
   </si>
   <si>
     <t>Engineer, Bard, Cyborg, Cleric, Merchant</t>
+  </si>
+  <si>
+    <t>Biome enemy differentiation: BiomeData.biomeEnemies list is populated but not used to change which enemies spawn per biome</t>
+  </si>
+  <si>
+    <t>Graveyard full logic: isInsideGraveyard only boosts enemy speed; intended graveyard mechanics are undefined</t>
+  </si>
+  <si>
+    <r>
+      <t>Character art</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: only Mage and Ranger have sprites; 36 of 38 classes have no art or unique logic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>More enemy types</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 86+ behaviors still fall through to default Chaser (only 4 new ones added)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VIP ad integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: "Watch Ad" button grants VIP immediately — needs a real ad SDK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Projectile prefabs for weapons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>WeaponSystem.Fire()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> warns if no </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>projectilePrefab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> assigned — the card pool items need prefab references set in the Inspector or created procedurally</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>More POI types</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: only 3 of 20 POI types have implemented logic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ultFill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> Slider legacy field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>SurvivorMasterScript</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> has dead </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Slider ultFill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> references that can be cleaned up once UI is confirmed wired through </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>GameHUD</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1675,6 +1840,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1708,10 +1903,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1740,8 +1936,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2019,6 +2225,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="86.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="22.8">
+      <c r="A4" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="28.8">
+      <c r="A6" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="28.8">
+      <c r="A7" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="22.8">
+      <c r="A8" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" display="vscode-file://vscode-app/c:/Users/mtgra/AppData/Local/Programs/Microsoft VS Code/cfbea10c5f/resources/app/out/vs/code/electron-browser/workbench/workbench.html" xr:uid="{E29E179C-DFD3-41BA-B6D7-4509C9B56477}"/>
+    <hyperlink ref="A7" r:id="rId2" display="vscode-file://vscode-app/c:/Users/mtgra/AppData/Local/Programs/Microsoft VS Code/cfbea10c5f/resources/app/out/vs/code/electron-browser/workbench/workbench.html" xr:uid="{CE4F124B-4CD6-40B6-8109-3C4CB64AA89D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD60BB66-895D-4009-B2A1-9C303AD5B319}">
   <dimension ref="A1:A114"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2134,45 +2398,45 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" hidden="1">
       <c r="A32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" hidden="1">
       <c r="A33" s="4"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" hidden="1">
       <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" hidden="1">
       <c r="A35" s="4"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" hidden="1">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" hidden="1">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" hidden="1">
       <c r="A38" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" hidden="1">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" hidden="1">
       <c r="A40" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" hidden="1">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" hidden="1">
       <c r="A42" s="5" t="s">
         <v>18</v>
       </c>
@@ -2440,7 +2704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57E82AF-136C-4B63-A787-571E3EBC6DD6}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="38.77734375" defaultRowHeight="14.4"/>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203F19B8-047B-4FA1-BC68-F024B6266A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1833281D-C0EE-4EA2-8F2B-D866A543BB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
+    <sheet name="Characters" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="162">
   <si>
     <t>Biome enemy differentiation: BiomeData.biomeEnemies list is populated but not used to change which enemies spawn per biome</t>
   </si>
@@ -49,13 +50,475 @@
   </si>
   <si>
     <t>ultFill Slider legacy field: SurvivorMasterScript has dead Slider ultFill references that can be cleaned up once UI is confirmed wired through GameHUD</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Paladin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alchemist</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Merchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Berserker</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ghost</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vampire</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Samurai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sniper</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Monk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Druid</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cyborg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cleric</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pyromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cryomancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ranger</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Warlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gladiator</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tactician</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shapeshifter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TimeMage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VoidCaller</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Beastmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NecroKnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ArcaneArcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PlagueDoctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gunslinger</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Viking</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Onmyoji</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Junker</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PuppetMaster</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Graveyard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Forge</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HolyShrine</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CursedAltar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ManaWell</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MerchantCart</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AncientLibrary</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HealingSpring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ScrapHeap</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VolcanicVent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FrozenObelisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ThievesDen</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Monolith</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Beehive</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RadarStation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ToxicPit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GoldenStatue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TimeRift</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Overgrowth</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Meteorite</t>
+  </si>
+  <si>
+    <t>POI</t>
+  </si>
+  <si>
+    <t>Chaser</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Charger</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tank</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Exploder</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shaman</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Freezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Swarmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ShieldBearer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BlackHole</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Commander</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mimic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Linker</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reflector</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Burrower</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Magnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Puffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jockey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mortar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siren</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gambler</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Webber</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Medic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SlimeQueen</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WindSpirit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GoldGrit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Glitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MimicChest</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sandworm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Silencer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gravitron</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SplitterCell</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ParasiteSeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FogWeaver</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MirrorShield</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LeadFoot</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finality</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Orbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MagnetRepel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ZigZagger</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bouncer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Anchor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SmokeBomb</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jammer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SniperElite</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Flashbanger</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Curver</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RustAura</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> XPLeech</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Coolant</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WeightLifter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TaxCollector</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inverter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ScreenGlitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GhostWriter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LagSpirit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cheerleader</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Totem</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FlagBearer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Landmine</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SporeCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IceCube</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TarPit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Meteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Paradox</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Collector</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reanimator</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TimeLooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MimicUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pacifist</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GlassCannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Blackout</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Puppeteer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Firewall</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GreedyKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Speedster</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Juggernaut</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SwarmLord</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VampireBat</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nemesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dev</t>
+  </si>
+  <si>
+    <t>Enemies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,13 +538,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -96,12 +586,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,4 +929,704 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64264F5C-371B-4B50-8094-51A73536206D}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C62" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C63" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C64" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C69" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C70" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1833281D-C0EE-4EA2-8F2B-D866A543BB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A944203C-7D78-4145-89B7-59230B09F38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
     <sheet name="Characters" sheetId="6" r:id="rId2"/>
+    <sheet name="Weapons" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,31 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="162">
-  <si>
-    <t>Biome enemy differentiation: BiomeData.biomeEnemies list is populated but not used to change which enemies spawn per biome</t>
-  </si>
-  <si>
-    <t>Graveyard full logic: isInsideGraveyard only boosts enemy speed; intended graveyard mechanics are undefined</t>
-  </si>
-  <si>
-    <t>Character art: only Mage and Ranger have sprites; 36 of 38 classes have no art or unique logic</t>
-  </si>
-  <si>
-    <t>More enemy types: 86+ behaviors still fall through to default Chaser (only 4 new ones added)</t>
-  </si>
-  <si>
-    <t>VIP ad integration: "Watch Ad" button grants VIP immediately — needs a real ad SDK</t>
-  </si>
-  <si>
-    <t>Projectile prefabs for weapons: WeaponSystem.Fire() warns if no projectilePrefab assigned — the card pool items need prefab references set in the Inspector or created procedurally</t>
-  </si>
-  <si>
-    <t>More POI types: only 3 of 20 POI types have implemented logic</t>
-  </si>
-  <si>
-    <t>ultFill Slider legacy field: SurvivorMasterScript has dead Slider ultFill references that can be cleaned up once UI is confirmed wired through GameHUD</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="208">
   <si>
     <t>Knight</t>
   </si>
@@ -512,27 +489,177 @@
   </si>
   <si>
     <t>Enemies</t>
+  </si>
+  <si>
+    <t>Sprites</t>
+  </si>
+  <si>
+    <t>Ads</t>
+  </si>
+  <si>
+    <t>Unique Enemy Movement</t>
+  </si>
+  <si>
+    <t>Evolutions</t>
+  </si>
+  <si>
+    <t>POI Graphics &amp; Abilites &amp; Fade Text upon entering</t>
+  </si>
+  <si>
+    <t>Cleanup unused code fragments</t>
+  </si>
+  <si>
+    <t>Unique Weapon Attacks</t>
+  </si>
+  <si>
+    <t>Game Modes</t>
+  </si>
+  <si>
+    <t>Wand</t>
+  </si>
+  <si>
+    <t>Hunter's Bow</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>Flame</t>
+  </si>
+  <si>
+    <t>Twin Daggers</t>
+  </si>
+  <si>
+    <t>Death Skull</t>
+  </si>
+  <si>
+    <t>War Hammer</t>
+  </si>
+  <si>
+    <t>Sentry Gun</t>
+  </si>
+  <si>
+    <t>Acid Flask</t>
+  </si>
+  <si>
+    <t>Gold Coin</t>
+  </si>
+  <si>
+    <t>Spectral Beam</t>
+  </si>
+  <si>
+    <t>Blood Fang</t>
+  </si>
+  <si>
+    <t>Katana</t>
+  </si>
+  <si>
+    <t>Music Note</t>
+  </si>
+  <si>
+    <t>Sniper Rifle</t>
+  </si>
+  <si>
+    <t>Iron Fist</t>
+  </si>
+  <si>
+    <t>Vine Whip</t>
+  </si>
+  <si>
+    <t>Chain Lightning</t>
+  </si>
+  <si>
+    <t>Holy Staff</t>
+  </si>
+  <si>
+    <t>Ice Shard</t>
+  </si>
+  <si>
+    <t>Eldritch Bolt</t>
+  </si>
+  <si>
+    <t>Assassin Blade</t>
+  </si>
+  <si>
+    <t>Trident</t>
+  </si>
+  <si>
+    <t>Pistol</t>
+  </si>
+  <si>
+    <t>Wolf Claws</t>
+  </si>
+  <si>
+    <t>Time Crystal</t>
+  </si>
+  <si>
+    <t>Void Orb</t>
+  </si>
+  <si>
+    <t>Hawk Call</t>
+  </si>
+  <si>
+    <t>Claymore</t>
+  </si>
+  <si>
+    <t>Arcane Arrow</t>
+  </si>
+  <si>
+    <t>Plague Canister</t>
+  </si>
+  <si>
+    <t>Dual Revolvers</t>
+  </si>
+  <si>
+    <t>Throwing Axe</t>
+  </si>
+  <si>
+    <t>Scrap Maul</t>
+  </si>
+  <si>
+    <t>Oracle Beam</t>
+  </si>
+  <si>
+    <t>Shadow Clone</t>
+  </si>
+  <si>
+    <t>Spirit Aura</t>
+  </si>
+  <si>
+    <t>Caltrop Throw</t>
+  </si>
+  <si>
+    <t>Tidal Bolt</t>
+  </si>
+  <si>
+    <t>Holy Scepter (Wand + Empty Tome)</t>
+  </si>
+  <si>
+    <t>Death Spiral (Axe + Heavy Bracers)</t>
+  </si>
+  <si>
+    <t>Supernova (Flame + Mana Well)</t>
+  </si>
+  <si>
+    <t>Sword of Fire (Sword + Flame)</t>
+  </si>
+  <si>
+    <t>Base Weapons</t>
+  </si>
+  <si>
+    <t>Evolution Level 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -560,7 +687,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -570,6 +697,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,17 +727,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,49 +1017,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="108.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
+      <c r="A6" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -936,697 +1073,933 @@
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>161</v>
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>11</v>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>79</v>
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>80</v>
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>81</v>
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>21</v>
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>65</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>18</v>
+      <c r="A21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>84</v>
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C35" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C36" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C37" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C38" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C39" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="4" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="4" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="4" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="4" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="4" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="4" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C41" s="4" t="s">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C42" s="4" t="s">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C43" s="4" t="s">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C44" s="4" t="s">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C45" s="4" t="s">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="4" t="s">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C47" s="4" t="s">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C48" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" s="4" t="s">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" s="4" t="s">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="4" t="s">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C52" s="4" t="s">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C60" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="4" t="s">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="4" t="s">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C62" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C55" s="4" t="s">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C63" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C56" s="4" t="s">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C64" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C57" s="4" t="s">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C58" s="4" t="s">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C59" s="4" t="s">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C60" s="4" t="s">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C61" s="4" t="s">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C69" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C62" s="4" t="s">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C70" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C63" s="4" t="s">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C64" s="4" t="s">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C65" s="4" t="s">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C66" s="4" t="s">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C67" s="4" t="s">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C68" s="4" t="s">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C69" s="4" t="s">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C70" s="4" t="s">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C71" s="4" t="s">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C72" s="4" t="s">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C73" s="4" t="s">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C74" s="4" t="s">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C75" s="4" t="s">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C76" s="4" t="s">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C77" s="4" t="s">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C78" s="4" t="s">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C79" s="4" t="s">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C80" s="4" t="s">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C81" s="4" t="s">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C82" s="4" t="s">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C83" s="4" t="s">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C84" s="4" t="s">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C85" s="4" t="s">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C86" s="4" t="s">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C87" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C88" s="4" t="s">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C89" s="4" t="s">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C90" s="4" t="s">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C91" s="4" t="s">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C92" s="4" t="s">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C93" s="4" t="s">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="1" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C94" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C95" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C96" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C97" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C98" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C99" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C100" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C101" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A979FDA-EB4F-4589-BF10-3AECB159F829}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A944203C-7D78-4145-89B7-59230B09F38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69B4977-D748-43C8-BCF1-C6114002C8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1134,7 +1134,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1145,7 +1145,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1156,7 +1156,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1167,7 +1167,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1211,7 +1211,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1233,7 +1233,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1244,7 +1244,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1266,7 +1266,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1334,7 +1334,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1390,7 +1390,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -1414,7 +1414,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -1430,7 +1430,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4521DC02-D967-4E5E-94DA-5287CE69E982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52DAEB9-D3AC-441F-B0C7-CA38E48ED754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -896,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -910,6 +910,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2168,7 +2169,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>168</v>
       </c>
       <c r="B26" t="s">
@@ -2245,7 +2246,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>167</v>
       </c>
       <c r="B33" t="s">
@@ -2355,7 +2356,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>175</v>
       </c>
       <c r="B43" t="s">
@@ -2366,7 +2367,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B44" t="s">

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52DAEB9-D3AC-441F-B0C7-CA38E48ED754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CC9C69-AA0A-4926-AF5B-4112DD15A2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
     <sheet name="Enemies" sheetId="6" r:id="rId2"/>
     <sheet name="POI" sheetId="9" r:id="rId3"/>
     <sheet name="Weapons Audit" sheetId="8" r:id="rId4"/>
+    <sheet name="Ideas" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="345">
   <si>
     <t>Knight</t>
   </si>
@@ -814,13 +815,871 @@
   </si>
   <si>
     <t>OracleBeam</t>
+  </si>
+  <si>
+    <t>1. The Virus (Infection Mode)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You don't collect weapons; you collect </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pathogens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Your "projectiles" are contagious. When you hit an enemy, they don't die instantly—they become infected and start damaging nearby enemies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have to manage the "Spread Rate" vs. "Lethality." If the virus kills too fast, it won't spread to the rest of the swarm. If it's too slow, you'll be overwhelmed.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Sigil Architect (Modular Rituals)</t>
+  </si>
+  <si>
+    <t>This mode turns the ground itself into your weapon.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You don't fire traditional projectiles. Instead, you drop "Connectors" and "Power Bricks" as you move.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> When you complete a closed geometric shape (like a square or triangle) on the ground, a ritual triggers within that area, obliterating everything inside.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Gameplay Impact:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> It becomes a game of "Snake" mixed with a survivors-like. You are constantly trying to pathfind around enemies to close your shapes without getting trapped.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Magnetic North</t>
+  </si>
+  <si>
+    <t>All XP gems and items are magnetic. If you move too fast, they trail behind you, forming a massive "tail." If enemies touch the tail, they absorb the XP and evolve into Elites.</t>
+  </si>
+  <si>
+    <t>4. Auction House (Economy Mode)</t>
+  </si>
+  <si>
+    <t>Experience points (XP) are replaced with a currency that fluctuates in value.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Every 3 minutes, the game pauses for a "Blind Auction."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Powerful items are put up for bid against "AI Rivals" who are also in the map with you. Do you spend all your gold on one Tier-5 weapon now, or save up for the endgame?</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Temporal Echoes (The Time-Loop Mode)</t>
+  </si>
+  <si>
+    <t>The run is divided into short 2-minute loops that stack on top of each other.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> When the 2-minute timer hits zero, you are sent back to the start. However, a "Ghost Echo" of your previous run is now playing alongside you, performing the exact movements and shots you did in the last loop.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> By the 10th loop, there are 10 versions of you on screen. The enemy count scales exponentially to compensate.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Gameplay Impact:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have to plan your movements in early loops to "cover" yourself for future loops (e.g., "In Loop 1, I'll clear the left side so that in Loop 5, my past self is protecting my flank").</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Shifting Biomes (The Maze Runner)</t>
+  </si>
+  <si>
+    <t>The map is a grid of rooms that physically shift and rearrange every 60 seconds.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You might be in an open field one moment and a narrow corridor the next.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You can see the "next layout" on a minimap. You must position yourself so you don't get crushed by a wall or trapped in a room full of Elites when the shift happens.</t>
+    </r>
+  </si>
+  <si>
+    <t>7. Roulette Weapons</t>
+  </si>
+  <si>
+    <t>Every time you reload or fire X shots, your weapon randomly swaps to a different one in your inventory. You have to build for "generalist" buffs rather than specific weapon synergies.</t>
+  </si>
+  <si>
+    <t>8. The Bodyguard (VIP Escort)</t>
+  </si>
+  <si>
+    <t>You are invincible, but you are protecting a "Client" who is very fragile.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The Client has terrible AI—they wander toward shiny objects and run away from you if you get too close.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Your weapons aren't just for killing; they are for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>crowd control</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. You use knockback and walls to "funnel" the Client toward the exit.</t>
+    </r>
+  </si>
+  <si>
+    <t>10. Shared Pool (Co-op/Versus)</t>
+  </si>
+  <si>
+    <t>You and a rival AI share the same upgrade pool. If the AI picks the "Chain Lightning," it's gone from your draft options forever.</t>
+  </si>
+  <si>
+    <t>14. The Slime Trail</t>
+  </si>
+  <si>
+    <t>You leave a trail of "acid" or "slow" behind you.</t>
+  </si>
+  <si>
+    <t>9. The Shadow (Stalker Mode)</t>
+  </si>
+  <si>
+    <t>An invincible, slow-moving "Shadow" of the player follows you at all times.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> It copies your current build. If you have "Chain Lightning," the Shadow also emits "Chain Lightning."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If it touches you, the run ends. You have to balance making yourself powerful enough to kill enemies, but not so powerful that your Shadow becomes impossible to kite.</t>
+    </r>
+  </si>
+  <si>
+    <t>11. Gravity Well</t>
+  </si>
+  <si>
+    <t>The center of the map has a massive gravitational pull.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> All projectiles, enemies, and XP gems curve toward the center.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You can use the gravity to "slingshot" your shots around corners, but staying near the edges makes you move slower as you fight the pull.</t>
+    </r>
+  </si>
+  <si>
+    <t>12. The Architect (Tower Defense)</t>
+  </si>
+  <si>
+    <t>You cannot move. Instead, you click to place traps and turrets.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have a limited "Energy" pool that refills when enemies die.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You can "possess" one of your turrets for 10 seconds to fire it manually with increased damage.</t>
+    </r>
+  </si>
+  <si>
+    <t>13. Blood Magic</t>
+  </si>
+  <si>
+    <t>You don't have a mana or cooldown system. Everything costs health.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Your primary way to heal is by standing in the "blood splatter" left by defeated enemies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The more health you lose, the higher your damage multiplier becomes, encouraging a high-risk "glass cannon" playstyle.</t>
+    </r>
+  </si>
+  <si>
+    <t>15. Minimalist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You can only have </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>one</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> weapon and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>one</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> passive buff at a time.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Every time you level up, you </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>must</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> replace your current item with a new one.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Items scale aggressively. A Level 10 "Basic Pistol" might be stronger than a Level 1 "God Slayer Sword," forcing you to decide when to break your synergy for raw power.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16. Nano-Swarm:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Instead of a character, you play as a cloud of nanites. You "attack" by overlapping with enemies, but your "health" is the literal size of your swarm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17. Darkness Visible:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The screen is pitch black except for a small radius around you. Enemies only become visible when they are hit by your "radar" pulse or enter your light circle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>18. Floor is Lava:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You can only stand on "safe tiles" that disappear after 5 seconds. You must constantly move to new platforms while fighting the horde.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>19. Recoil Propulsion:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have no movement keys. The only way to move is by using the recoil of your weapons to push yourself in the opposite direction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>20. Boss Rush:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> There are no "trash mobs." Every 30 seconds, a mini-boss spawns. You are constantly fighting 3–4 bosses at once with unique mechanics.</t>
+    </r>
+  </si>
+  <si>
+    <t>21. The Pacifist</t>
+  </si>
+  <si>
+    <t>You cannot deal damage directly.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have an "Aura of Conversion." Enemies that stay inside your radius for 3 seconds become your allies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You have to keep your "converted" army alive. If your army dies, you have no way to defend yourself while you "recruit" more.</t>
+    </r>
+  </si>
+  <si>
+    <t>22. Rhythm Heaven (Beat-Based)</t>
+  </si>
+  <si>
+    <t>Your weapons only fire on the beat of the background music.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Perfect timing increases your damage and fire rate.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Missing the beat cause your weapon to "jam" for 2 seconds, leaving you vulnerable.</t>
+    </r>
+  </si>
+  <si>
+    <t>23. The Alchemist (Crafting Mode)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You don't get weapons from leveling up. You get </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Fire, Water, Iron, Glass).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You must manually combine elements in a crafting menu to create spells (e.g., Fire + Glass = Flaming Shards).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Recipes change every run. You have to spend the first 5 minutes "experimenting" to find the most powerful combinations for that specific run.</t>
+    </r>
+  </si>
+  <si>
+    <t>24. Size Matters</t>
+  </si>
+  <si>
+    <t>Every time you kill an enemy, you grow 1% larger.</t>
+  </si>
+  <si>
+    <r>
+      <t>The Hook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Being larger increases your health and reach.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Twist:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> As you grow, you become a bigger target, move slower, and eventually, you can't fit through narrow gaps in the map, forcing you to stay in open areas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>25. The Curator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Instead of a standard skill tree, you unlock "Exhibit Halls" in a museum. Each hall you fill with "Artifacts" (rare drops from bosses) provides permanent stat boosts to specific modes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>26. Mode Fusion:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Once you beat any two modes, you can "Fuse" them for a Nightmare Run (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>The Shadow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Floor is Lava</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>27. The Stock Market:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You can "invest" your meta-currency into different weapon manufacturers. If players globally use the "Shotgun" more this week, the "Shotgun Company" stock goes up, granting you better starting bonuses for those weapons.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>28. Community Challenges:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Every weekend, the developer picks a specific "Seed" and "Mode Combination." Everyone competes on a global leaderboard for a unique cosmetic skin.</t>
+    </r>
+  </si>
+  <si>
+    <t>Core Game Modes</t>
+  </si>
+  <si>
+    <t>Unique Combat &amp; Movement Mechanics</t>
+  </si>
+  <si>
+    <t>Advanced Interaction Modes</t>
+  </si>
+  <si>
+    <t>Meta-Progression &amp; Hub Features</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,6 +1709,40 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -896,7 +1789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -910,6 +1803,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2026,7 +2931,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="11" t="s">
         <v>202</v>
       </c>
       <c r="B13" t="s">
@@ -2169,7 +3074,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="A26" t="s">
         <v>168</v>
       </c>
       <c r="B26" t="s">
@@ -2202,7 +3107,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="11" t="s">
         <v>230</v>
       </c>
       <c r="B29" t="s">
@@ -2246,7 +3151,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="A33" t="s">
         <v>167</v>
       </c>
       <c r="B33" t="s">
@@ -2345,7 +3250,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="11" t="s">
         <v>174</v>
       </c>
       <c r="B42" t="s">
@@ -2356,7 +3261,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="A43" t="s">
         <v>175</v>
       </c>
       <c r="B43" t="s">
@@ -2367,7 +3272,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
+      <c r="A44" t="s">
         <v>177</v>
       </c>
       <c r="B44" t="s">
@@ -2397,6 +3302,432 @@
       </c>
       <c r="C46" t="s">
         <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
+  <dimension ref="A1:A86"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CC9C69-AA0A-4926-AF5B-4112DD15A2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBAA7C8-408C-4CBC-A33A-3BAB3C145728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="358">
   <si>
     <t>Knight</t>
   </si>
@@ -1673,6 +1673,45 @@
   </si>
   <si>
     <t>Meta-Progression &amp; Hub Features</t>
+  </si>
+  <si>
+    <t>Psammomancer</t>
+  </si>
+  <si>
+    <t>Sand Shield</t>
+  </si>
+  <si>
+    <t>SandShield</t>
+  </si>
+  <si>
+    <t>Hivemaster</t>
+  </si>
+  <si>
+    <t>InsectSwarm</t>
+  </si>
+  <si>
+    <t>Insect Swarm</t>
+  </si>
+  <si>
+    <t>Geomancer</t>
+  </si>
+  <si>
+    <t>Aeromancer</t>
+  </si>
+  <si>
+    <t>Meteor Smash</t>
+  </si>
+  <si>
+    <t>MeteorSmash</t>
+  </si>
+  <si>
+    <t>Wind Storm</t>
+  </si>
+  <si>
+    <t>WindStorm</t>
+  </si>
+  <si>
+    <t>TimeManipulation</t>
   </si>
 </sst>
 </file>
@@ -2790,7 +2829,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134B62F-E2D3-4D00-ACEE-B088AA598477}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -2920,7 +2959,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="11" t="s">
         <v>201</v>
       </c>
       <c r="B12" t="s">
@@ -2931,7 +2970,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" t="s">
         <v>202</v>
       </c>
       <c r="B13" t="s">
@@ -3092,11 +3131,11 @@
         <v>227</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="11" t="s">
         <v>229</v>
       </c>
       <c r="B28" t="s">
@@ -3107,7 +3146,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" t="s">
         <v>230</v>
       </c>
       <c r="B29" t="s">
@@ -3206,7 +3245,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="11" t="s">
         <v>172</v>
       </c>
       <c r="B38" t="s">
@@ -3228,7 +3267,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="11" t="s">
         <v>173</v>
       </c>
       <c r="B40" t="s">
@@ -3250,7 +3289,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" t="s">
         <v>174</v>
       </c>
       <c r="B42" t="s">
@@ -3283,7 +3322,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="11" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
@@ -3302,6 +3341,50 @@
       </c>
       <c r="C46" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBAA7C8-408C-4CBC-A33A-3BAB3C145728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57522F67-C364-4005-A8B4-C585D1C5B9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="361">
   <si>
     <t>Knight</t>
   </si>
@@ -1712,6 +1712,15 @@
   </si>
   <si>
     <t>TimeManipulation</t>
+  </si>
+  <si>
+    <t>User Habit Tracker</t>
+  </si>
+  <si>
+    <t>Stats Tracking (Damage over time by weapon, number of kills, etc.)</t>
+  </si>
+  <si>
+    <t>Custom Attack Logic</t>
   </si>
 </sst>
 </file>
@@ -1828,7 +1837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1855,6 +1864,7 @@
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2135,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -2179,6 +2189,16 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2829,15 +2849,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134B62F-E2D3-4D00-ACEE-B088AA598477}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2847,8 +2868,11 @@
       <c r="C1" s="4" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -2858,8 +2882,9 @@
       <c r="C2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>186</v>
       </c>
@@ -2870,7 +2895,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2880,8 +2905,9 @@
       <c r="C4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>188</v>
       </c>
@@ -2891,9 +2917,10 @@
       <c r="C5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>189</v>
       </c>
       <c r="B6" t="s">
@@ -2902,8 +2929,9 @@
       <c r="C6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -2914,7 +2942,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -2924,8 +2952,9 @@
       <c r="C8" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>195</v>
       </c>
@@ -2936,7 +2965,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -2947,7 +2976,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -2958,8 +2987,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>201</v>
       </c>
       <c r="B12" t="s">
@@ -2969,7 +2998,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>202</v>
       </c>
@@ -2979,8 +3008,9 @@
       <c r="C13" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>204</v>
       </c>
@@ -2991,7 +3021,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>207</v>
       </c>
@@ -3002,7 +3032,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>208</v>
       </c>
@@ -3013,7 +3043,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>210</v>
       </c>
@@ -3024,7 +3054,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>212</v>
       </c>
@@ -3034,8 +3064,9 @@
       <c r="C18" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>214</v>
       </c>
@@ -3046,7 +3077,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>216</v>
       </c>
@@ -3057,7 +3088,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>218</v>
       </c>
@@ -3068,7 +3099,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>220</v>
       </c>
@@ -3079,7 +3110,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>222</v>
       </c>
@@ -3089,8 +3120,9 @@
       <c r="C23" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>224</v>
       </c>
@@ -3101,7 +3133,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>226</v>
       </c>
@@ -3112,7 +3144,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>168</v>
       </c>
@@ -3123,7 +3155,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>181</v>
       </c>
@@ -3134,8 +3166,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>229</v>
       </c>
       <c r="B28" t="s">
@@ -3144,8 +3176,9 @@
       <c r="C28" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>230</v>
       </c>
@@ -3156,7 +3189,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>232</v>
       </c>
@@ -3166,8 +3199,9 @@
       <c r="C30" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>234</v>
       </c>
@@ -3177,8 +3211,9 @@
       <c r="C31" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>236</v>
       </c>
@@ -3189,7 +3224,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>167</v>
       </c>
@@ -3200,7 +3235,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>238</v>
       </c>
@@ -3211,7 +3246,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>240</v>
       </c>
@@ -3222,8 +3257,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
         <v>171</v>
       </c>
       <c r="B36" t="s">
@@ -3232,8 +3267,9 @@
       <c r="C36" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="12"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>242</v>
       </c>
@@ -3244,8 +3280,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>172</v>
       </c>
       <c r="B38" t="s">
@@ -3255,7 +3291,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>176</v>
       </c>
@@ -3266,8 +3302,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>173</v>
       </c>
       <c r="B40" t="s">
@@ -3277,7 +3313,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>179</v>
       </c>
@@ -3288,7 +3324,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>174</v>
       </c>
@@ -3299,7 +3335,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -3310,7 +3346,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>177</v>
       </c>
@@ -3320,9 +3356,10 @@
       <c r="C44" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
@@ -3332,7 +3369,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>247</v>
       </c>
@@ -3343,8 +3380,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>345</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -3354,7 +3391,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>348</v>
       </c>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57522F67-C364-4005-A8B4-C585D1C5B9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5092DF5A-7AF7-479A-8FD9-80086E25A90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="132" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="358">
   <si>
     <t>Knight</t>
   </si>
@@ -571,9 +571,6 @@
     <t>ArcticScout</t>
   </si>
   <si>
-    <t>Psychic</t>
-  </si>
-  <si>
     <t>Chronomancer</t>
   </si>
   <si>
@@ -770,12 +767,6 @@
   </si>
   <si>
     <t>Tidal Wave</t>
-  </si>
-  <si>
-    <t>Psychomancer</t>
-  </si>
-  <si>
-    <t>Psychic Blast</t>
   </si>
   <si>
     <t>Downpour</t>
@@ -1863,8 +1854,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2193,12 +2184,12 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2739,7 +2730,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2849,7 +2840,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134B62F-E2D3-4D00-ACEE-B088AA598477}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -2863,80 +2854,81 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" t="s">
         <v>184</v>
       </c>
-      <c r="B2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="12"/>
+      <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C4" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="12"/>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" t="s">
         <v>189</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>190</v>
       </c>
-      <c r="C6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
         <v>163</v>
@@ -2944,52 +2936,52 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" t="s">
         <v>193</v>
       </c>
-      <c r="B8" t="s">
-        <v>253</v>
-      </c>
-      <c r="C8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
         <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
         <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
         <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
@@ -3000,30 +2992,30 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
         <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" s="12"/>
+        <v>256</v>
+      </c>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" t="s">
         <v>204</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>205</v>
-      </c>
-      <c r="C14" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
         <v>141</v>
@@ -3034,108 +3026,108 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" t="s">
         <v>208</v>
-      </c>
-      <c r="B16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C16" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
         <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" t="s">
         <v>212</v>
       </c>
-      <c r="B18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" t="s">
         <v>214</v>
-      </c>
-      <c r="B19" t="s">
-        <v>250</v>
-      </c>
-      <c r="C19" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s">
         <v>216</v>
       </c>
-      <c r="B20" t="s">
-        <v>217</v>
-      </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s">
         <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
         <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
         <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D23" s="12"/>
+        <v>222</v>
+      </c>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s">
         <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s">
         <v>147</v>
@@ -3157,71 +3149,71 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s">
         <v>149</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D28" s="12"/>
+        <v>257</v>
+      </c>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B29" t="s">
         <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" t="s">
         <v>232</v>
       </c>
-      <c r="B30" t="s">
-        <v>233</v>
-      </c>
       <c r="C30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D30" s="12"/>
+        <v>232</v>
+      </c>
+      <c r="D30" s="11"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s">
         <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>235</v>
-      </c>
-      <c r="D31" s="12"/>
+        <v>234</v>
+      </c>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s">
         <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -3232,52 +3224,52 @@
         <v>152</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
         <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s">
         <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" t="s">
         <v>171</v>
       </c>
       <c r="B36" t="s">
         <v>155</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
-      </c>
-      <c r="D36" s="12"/>
+        <v>258</v>
+      </c>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B37" t="s">
         <v>156</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -3285,18 +3277,18 @@
         <v>172</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="12" t="s">
         <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
         <v>160</v>
@@ -3318,7 +3310,7 @@
         <v>179</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C41" t="s">
         <v>162</v>
@@ -3340,7 +3332,7 @@
         <v>175</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C43" t="s">
         <v>165</v>
@@ -3351,12 +3343,12 @@
         <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C44" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="12"/>
+      <c r="D44" s="11"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -3368,60 +3360,50 @@
       <c r="C45" t="s">
         <v>169</v>
       </c>
+      <c r="D45" s="11"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B46" t="s">
-        <v>248</v>
-      </c>
-      <c r="C46" t="s">
-        <v>180</v>
+      <c r="A46" t="s">
+        <v>342</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="12" t="s">
         <v>345</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>347</v>
-      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="12" t="s">
         <v>348</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>350</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3437,417 +3419,417 @@
   <sheetData>
     <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5092DF5A-7AF7-479A-8FD9-80086E25A90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4646D8FD-42F2-427B-993D-DF10B4FADEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="132" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="364">
   <si>
     <t>Knight</t>
   </si>
@@ -1712,6 +1712,24 @@
   </si>
   <si>
     <t>Custom Attack Logic</t>
+  </si>
+  <si>
+    <t>Dimension Master</t>
+  </si>
+  <si>
+    <t>Teleportation Strike</t>
+  </si>
+  <si>
+    <t>TeleportationStrike</t>
+  </si>
+  <si>
+    <t>Gravity Manipulator</t>
+  </si>
+  <si>
+    <t>Gravity Well</t>
+  </si>
+  <si>
+    <t>GravityWell</t>
   </si>
 </sst>
 </file>
@@ -2840,10 +2858,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134B62F-E2D3-4D00-ACEE-B088AA598477}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -2912,7 +2930,7 @@
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="12" t="s">
         <v>188</v>
       </c>
       <c r="B6" t="s">
@@ -3148,7 +3166,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="12" t="s">
         <v>180</v>
       </c>
       <c r="B27" t="s">
@@ -3262,7 +3280,7 @@
       <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="12" t="s">
         <v>241</v>
       </c>
       <c r="B37" t="s">
@@ -3284,7 +3302,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" t="s">
         <v>176</v>
       </c>
       <c r="B39" t="s">
@@ -3306,7 +3324,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="12" t="s">
         <v>179</v>
       </c>
       <c r="B41" t="s">
@@ -3374,7 +3392,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
+      <c r="A47" t="s">
         <v>345</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -3385,7 +3403,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="12" t="s">
+      <c r="A48" t="s">
         <v>348</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -3396,7 +3414,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="12" t="s">
         <v>349</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -3404,6 +3422,28 @@
       </c>
       <c r="C49" s="6" t="s">
         <v>353</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4646D8FD-42F2-427B-993D-DF10B4FADEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="132" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -1846,7 +1846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1873,7 +1873,6 @@
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2930,7 +2929,7 @@
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" t="s">
         <v>188</v>
       </c>
       <c r="B6" t="s">
@@ -3166,7 +3165,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" t="s">
         <v>180</v>
       </c>
       <c r="B27" t="s">
@@ -3280,7 +3279,7 @@
       <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
+      <c r="A37" t="s">
         <v>241</v>
       </c>
       <c r="B37" t="s">
@@ -3324,7 +3323,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
+      <c r="A41" t="s">
         <v>179</v>
       </c>
       <c r="B41" t="s">
@@ -3414,7 +3413,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="12" t="s">
+      <c r="A49" t="s">
         <v>349</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -3425,7 +3424,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="12" t="s">
+      <c r="A50" t="s">
         <v>358</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -3436,7 +3435,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="12" t="s">
+      <c r="A51" t="s">
         <v>361</v>
       </c>
       <c r="B51" s="6" t="s">

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4646D8FD-42F2-427B-993D-DF10B4FADEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B82FF5F-8F52-4EDC-8F69-0129BC2C6DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="304">
   <si>
     <t>Knight</t>
   </si>
@@ -808,864 +808,6 @@
     <t>OracleBeam</t>
   </si>
   <si>
-    <t>1. The Virus (Infection Mode)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">You don't collect weapons; you collect </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pathogens</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Your "projectiles" are contagious. When you hit an enemy, they don't die instantly—they become infected and start damaging nearby enemies.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have to manage the "Spread Rate" vs. "Lethality." If the virus kills too fast, it won't spread to the rest of the swarm. If it's too slow, you'll be overwhelmed.</t>
-    </r>
-  </si>
-  <si>
-    <t>2. Sigil Architect (Modular Rituals)</t>
-  </si>
-  <si>
-    <t>This mode turns the ground itself into your weapon.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You don't fire traditional projectiles. Instead, you drop "Connectors" and "Power Bricks" as you move.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> When you complete a closed geometric shape (like a square or triangle) on the ground, a ritual triggers within that area, obliterating everything inside.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Gameplay Impact:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> It becomes a game of "Snake" mixed with a survivors-like. You are constantly trying to pathfind around enemies to close your shapes without getting trapped.</t>
-    </r>
-  </si>
-  <si>
-    <t>3. Magnetic North</t>
-  </si>
-  <si>
-    <t>All XP gems and items are magnetic. If you move too fast, they trail behind you, forming a massive "tail." If enemies touch the tail, they absorb the XP and evolve into Elites.</t>
-  </si>
-  <si>
-    <t>4. Auction House (Economy Mode)</t>
-  </si>
-  <si>
-    <t>Experience points (XP) are replaced with a currency that fluctuates in value.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Every 3 minutes, the game pauses for a "Blind Auction."</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Powerful items are put up for bid against "AI Rivals" who are also in the map with you. Do you spend all your gold on one Tier-5 weapon now, or save up for the endgame?</t>
-    </r>
-  </si>
-  <si>
-    <t>5. Temporal Echoes (The Time-Loop Mode)</t>
-  </si>
-  <si>
-    <t>The run is divided into short 2-minute loops that stack on top of each other.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> When the 2-minute timer hits zero, you are sent back to the start. However, a "Ghost Echo" of your previous run is now playing alongside you, performing the exact movements and shots you did in the last loop.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> By the 10th loop, there are 10 versions of you on screen. The enemy count scales exponentially to compensate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Gameplay Impact:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have to plan your movements in early loops to "cover" yourself for future loops (e.g., "In Loop 1, I'll clear the left side so that in Loop 5, my past self is protecting my flank").</t>
-    </r>
-  </si>
-  <si>
-    <t>6. Shifting Biomes (The Maze Runner)</t>
-  </si>
-  <si>
-    <t>The map is a grid of rooms that physically shift and rearrange every 60 seconds.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You might be in an open field one moment and a narrow corridor the next.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You can see the "next layout" on a minimap. You must position yourself so you don't get crushed by a wall or trapped in a room full of Elites when the shift happens.</t>
-    </r>
-  </si>
-  <si>
-    <t>7. Roulette Weapons</t>
-  </si>
-  <si>
-    <t>Every time you reload or fire X shots, your weapon randomly swaps to a different one in your inventory. You have to build for "generalist" buffs rather than specific weapon synergies.</t>
-  </si>
-  <si>
-    <t>8. The Bodyguard (VIP Escort)</t>
-  </si>
-  <si>
-    <t>You are invincible, but you are protecting a "Client" who is very fragile.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The Client has terrible AI—they wander toward shiny objects and run away from you if you get too close.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Your weapons aren't just for killing; they are for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>crowd control</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. You use knockback and walls to "funnel" the Client toward the exit.</t>
-    </r>
-  </si>
-  <si>
-    <t>10. Shared Pool (Co-op/Versus)</t>
-  </si>
-  <si>
-    <t>You and a rival AI share the same upgrade pool. If the AI picks the "Chain Lightning," it's gone from your draft options forever.</t>
-  </si>
-  <si>
-    <t>14. The Slime Trail</t>
-  </si>
-  <si>
-    <t>You leave a trail of "acid" or "slow" behind you.</t>
-  </si>
-  <si>
-    <t>9. The Shadow (Stalker Mode)</t>
-  </si>
-  <si>
-    <t>An invincible, slow-moving "Shadow" of the player follows you at all times.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> It copies your current build. If you have "Chain Lightning," the Shadow also emits "Chain Lightning."</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> If it touches you, the run ends. You have to balance making yourself powerful enough to kill enemies, but not so powerful that your Shadow becomes impossible to kite.</t>
-    </r>
-  </si>
-  <si>
-    <t>11. Gravity Well</t>
-  </si>
-  <si>
-    <t>The center of the map has a massive gravitational pull.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> All projectiles, enemies, and XP gems curve toward the center.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You can use the gravity to "slingshot" your shots around corners, but staying near the edges makes you move slower as you fight the pull.</t>
-    </r>
-  </si>
-  <si>
-    <t>12. The Architect (Tower Defense)</t>
-  </si>
-  <si>
-    <t>You cannot move. Instead, you click to place traps and turrets.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have a limited "Energy" pool that refills when enemies die.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You can "possess" one of your turrets for 10 seconds to fire it manually with increased damage.</t>
-    </r>
-  </si>
-  <si>
-    <t>13. Blood Magic</t>
-  </si>
-  <si>
-    <t>You don't have a mana or cooldown system. Everything costs health.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Your primary way to heal is by standing in the "blood splatter" left by defeated enemies.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The more health you lose, the higher your damage multiplier becomes, encouraging a high-risk "glass cannon" playstyle.</t>
-    </r>
-  </si>
-  <si>
-    <t>15. Minimalist</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">You can only have </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>one</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> weapon and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>one</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> passive buff at a time.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Every time you level up, you </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>must</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> replace your current item with a new one.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Items scale aggressively. A Level 10 "Basic Pistol" might be stronger than a Level 1 "God Slayer Sword," forcing you to decide when to break your synergy for raw power.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>16. Nano-Swarm:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Instead of a character, you play as a cloud of nanites. You "attack" by overlapping with enemies, but your "health" is the literal size of your swarm.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>17. Darkness Visible:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The screen is pitch black except for a small radius around you. Enemies only become visible when they are hit by your "radar" pulse or enter your light circle.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>18. Floor is Lava:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You can only stand on "safe tiles" that disappear after 5 seconds. You must constantly move to new platforms while fighting the horde.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>19. Recoil Propulsion:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have no movement keys. The only way to move is by using the recoil of your weapons to push yourself in the opposite direction.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>20. Boss Rush:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> There are no "trash mobs." Every 30 seconds, a mini-boss spawns. You are constantly fighting 3–4 bosses at once with unique mechanics.</t>
-    </r>
-  </si>
-  <si>
-    <t>21. The Pacifist</t>
-  </si>
-  <si>
-    <t>You cannot deal damage directly.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have an "Aura of Conversion." Enemies that stay inside your radius for 3 seconds become your allies.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You have to keep your "converted" army alive. If your army dies, you have no way to defend yourself while you "recruit" more.</t>
-    </r>
-  </si>
-  <si>
-    <t>22. Rhythm Heaven (Beat-Based)</t>
-  </si>
-  <si>
-    <t>Your weapons only fire on the beat of the background music.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Perfect timing increases your damage and fire rate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Missing the beat cause your weapon to "jam" for 2 seconds, leaving you vulnerable.</t>
-    </r>
-  </si>
-  <si>
-    <t>23. The Alchemist (Crafting Mode)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">You don't get weapons from leveling up. You get </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Elements</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Fire, Water, Iron, Glass).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You must manually combine elements in a crafting menu to create spells (e.g., Fire + Glass = Flaming Shards).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Recipes change every run. You have to spend the first 5 minutes "experimenting" to find the most powerful combinations for that specific run.</t>
-    </r>
-  </si>
-  <si>
-    <t>24. Size Matters</t>
-  </si>
-  <si>
-    <t>Every time you kill an enemy, you grow 1% larger.</t>
-  </si>
-  <si>
-    <r>
-      <t>The Hook:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Being larger increases your health and reach.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>The Twist:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> As you grow, you become a bigger target, move slower, and eventually, you can't fit through narrow gaps in the map, forcing you to stay in open areas.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>25. The Curator:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Instead of a standard skill tree, you unlock "Exhibit Halls" in a museum. Each hall you fill with "Artifacts" (rare drops from bosses) provides permanent stat boosts to specific modes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>26. Mode Fusion:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Once you beat any two modes, you can "Fuse" them for a Nightmare Run (e.g., </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Shadow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Floor is Lava</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>27. The Stock Market:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You can "invest" your meta-currency into different weapon manufacturers. If players globally use the "Shotgun" more this week, the "Shotgun Company" stock goes up, granting you better starting bonuses for those weapons.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>28. Community Challenges:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Every weekend, the developer picks a specific "Seed" and "Mode Combination." Everyone competes on a global leaderboard for a unique cosmetic skin.</t>
-    </r>
-  </si>
-  <si>
-    <t>Core Game Modes</t>
-  </si>
-  <si>
-    <t>Unique Combat &amp; Movement Mechanics</t>
-  </si>
-  <si>
-    <t>Advanced Interaction Modes</t>
-  </si>
-  <si>
-    <t>Meta-Progression &amp; Hub Features</t>
-  </si>
-  <si>
     <t>Psammomancer</t>
   </si>
   <si>
@@ -1730,13 +872,82 @@
   </si>
   <si>
     <t>GravityWell</t>
+  </si>
+  <si>
+    <t>Infect Enemies and that hurts nearby enemies</t>
+  </si>
+  <si>
+    <t>Characters</t>
+  </si>
+  <si>
+    <t>Sigil Architect – The Character drops a trail behind them, and if they enclose the trail, the trail and all enemies within die/take damage</t>
+  </si>
+  <si>
+    <t>Parasite Enemies – Enemies can absorb  XP Gems and evolve into Elites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auction House – Every 3 minutes, the game pauses for a "Blind Auction." Powerful items are put up for bid against "AI Rivals" who are also in the map with you. </t>
+  </si>
+  <si>
+    <t>Temporal Echoes (The Time-Loop Mode) – The run is divided into short 2-minute loops that stack on top of each other. When the 2-minute timer hits zero, you are sent back to the start. However, a "Ghost Echo" of your previous run is now playing alongside you, performing the exact movements and shots you did in the last loop.</t>
+  </si>
+  <si>
+    <t>Shifting Biomes – The map is a grid of rooms that physically shift and rearrange every 60 seconds.</t>
+  </si>
+  <si>
+    <t>Roulette Weapons – Every 2 minutes, your weapons randomly swaps to different ones</t>
+  </si>
+  <si>
+    <t>The Bodyguard (VIP Escort) – You are invincible, but you are protecting a "Client" who is very fragile.</t>
+  </si>
+  <si>
+    <t>The Shadow – AI with your build spawns every 5 minutes. You must defeat them or lose</t>
+  </si>
+  <si>
+    <t>Shared Pool (Co-op/Versus) – You and a rival AI share the same upgrade pool. If the AI picks the "Chain Lightning," it's gone from your draft options forever.</t>
+  </si>
+  <si>
+    <t>Shared Pool (Co-op/Versus) – You and a rival PVP Player share the same upgrade pool. If the AI picks the "Chain Lightning," it's gone from your draft options forever.</t>
+  </si>
+  <si>
+    <t>Through The Looking Glass – PVP, one player spawns the waves of enemies from a budget, and the other plays the game normally</t>
+  </si>
+  <si>
+    <t>Gravity Well– The center of the map has a massive gravitational pull.</t>
+  </si>
+  <si>
+    <t>The Architect (Tower Defense)</t>
+  </si>
+  <si>
+    <t>lower health = higher damage</t>
+  </si>
+  <si>
+    <t>The Slime Trail – You leave a trail of "acid"  behind you.</t>
+  </si>
+  <si>
+    <t>Minimalist – You can only have one weapon and one passive buff at a time. Every time you level up, you must replace your current item with a new one.</t>
+  </si>
+  <si>
+    <t>Floor is Lava– You can only stand on "safe tiles" that disappear after 5 seconds. You must constantly move to new platforms while fighting the horde.</t>
+  </si>
+  <si>
+    <t>Boss Rush – Every 10 seconds, a mini-boss spawns. Every minute a boss spawns.</t>
+  </si>
+  <si>
+    <t>The Pacifist(Character) You cannot deal damage directly. You have an "Aura of Conversion." Enemies that stay inside your radius for 3 seconds become your allies.</t>
+  </si>
+  <si>
+    <t>Mode Fusion– Once you beat any two modes, you can "Fuse" them for a Nightmare Run (e.g., The Shadow + Floor is Lava).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Challenges– Every weekend, the developer picks a specific "Seed" and "Mode Combination." Everyone competes on a global leaderboard </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1766,40 +977,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.5"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1846,7 +1023,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1860,19 +1037,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2201,12 +1372,12 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2877,7 +2048,7 @@
         <v>182</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>357</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2890,7 +2061,7 @@
       <c r="C2" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -2902,7 +2073,7 @@
       <c r="C3" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -2914,7 +2085,7 @@
       <c r="C4" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -2926,7 +2097,7 @@
       <c r="C5" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -2938,7 +2109,7 @@
       <c r="C6" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -2961,7 +2132,7 @@
       <c r="C8" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -3017,7 +2188,7 @@
       <c r="C13" t="s">
         <v>256</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -3073,7 +2244,7 @@
       <c r="C18" t="s">
         <v>212</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -3129,7 +2300,7 @@
       <c r="C23" t="s">
         <v>222</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -3172,7 +2343,7 @@
         <v>226</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -3185,7 +2356,7 @@
       <c r="C28" t="s">
         <v>257</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -3208,7 +2379,7 @@
       <c r="C30" t="s">
         <v>232</v>
       </c>
-      <c r="D30" s="11"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -3220,7 +2391,7 @@
       <c r="C31" t="s">
         <v>234</v>
       </c>
-      <c r="D31" s="11"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -3276,7 +2447,7 @@
       <c r="C36" t="s">
         <v>258</v>
       </c>
-      <c r="D36" s="11"/>
+      <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -3365,7 +2536,7 @@
       <c r="C44" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="11"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -3377,72 +2548,72 @@
       <c r="C45" t="s">
         <v>169</v>
       </c>
-      <c r="D45" s="11"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>259</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>343</v>
+        <v>260</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>344</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>345</v>
+        <v>262</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>346</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>350</v>
+        <v>267</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>352</v>
+        <v>269</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>360</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>363</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3453,422 +2624,121 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
-  <dimension ref="A1:A86"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="80.21875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="9" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="8" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="9" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="9" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A77" s="10" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="8" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B82FF5F-8F52-4EDC-8F69-0129BC2C6DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C2F6B-401E-4411-BBF5-6C069DEFED2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
     <sheet name="Enemies" sheetId="6" r:id="rId2"/>
     <sheet name="POI" sheetId="9" r:id="rId3"/>
     <sheet name="Weapons Audit" sheetId="8" r:id="rId4"/>
-    <sheet name="Ideas" sheetId="10" r:id="rId5"/>
+    <sheet name="Biomes" sheetId="11" r:id="rId5"/>
+    <sheet name="Ideas" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="310">
   <si>
     <t>Knight</t>
   </si>
@@ -97,9 +98,6 @@
     <t xml:space="preserve"> Monolith</t>
   </si>
   <si>
-    <t xml:space="preserve"> Beehive</t>
-  </si>
-  <si>
     <t xml:space="preserve"> RadarStation</t>
   </si>
   <si>
@@ -941,6 +939,27 @@
   </si>
   <si>
     <t xml:space="preserve">Community Challenges– Every weekend, the developer picks a specific "Seed" and "Mode Combination." Everyone competes on a global leaderboard </t>
+  </si>
+  <si>
+    <t>1. Forest</t>
+  </si>
+  <si>
+    <t>2. Mountains</t>
+  </si>
+  <si>
+    <t>3. Volcano</t>
+  </si>
+  <si>
+    <t>4. River</t>
+  </si>
+  <si>
+    <t>5. Swamp</t>
+  </si>
+  <si>
+    <t>6. Plains</t>
+  </si>
+  <si>
+    <t>Jungle</t>
   </si>
 </sst>
 </file>
@@ -1332,52 +1351,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -1396,37 +1415,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -1436,17 +1455,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -1461,27 +1480,27 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
@@ -1491,7 +1510,7 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
@@ -1501,132 +1520,132 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
@@ -1636,192 +1655,192 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
@@ -1831,72 +1850,72 @@
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1915,110 +1934,110 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2031,7 +2050,7 @@
   <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -2042,36 +2061,36 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" t="s">
         <v>183</v>
-      </c>
-      <c r="B2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C2" t="s">
-        <v>184</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
         <v>185</v>
-      </c>
-      <c r="B3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" t="s">
-        <v>186</v>
       </c>
       <c r="D3" s="7"/>
     </row>
@@ -2080,540 +2099,540 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
         <v>188</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>189</v>
-      </c>
-      <c r="C6" t="s">
-        <v>190</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
         <v>192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" t="s">
-        <v>193</v>
       </c>
       <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
         <v>194</v>
-      </c>
-      <c r="B9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" t="s">
         <v>196</v>
-      </c>
-      <c r="B10" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
         <v>198</v>
-      </c>
-      <c r="B11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14" t="s">
         <v>203</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>204</v>
-      </c>
-      <c r="C14" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" t="s">
         <v>207</v>
-      </c>
-      <c r="B16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C16" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" t="s">
         <v>209</v>
-      </c>
-      <c r="B17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" t="s">
         <v>211</v>
-      </c>
-      <c r="B18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C18" t="s">
-        <v>212</v>
       </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" t="s">
         <v>213</v>
-      </c>
-      <c r="B19" t="s">
-        <v>247</v>
-      </c>
-      <c r="C19" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" t="s">
         <v>215</v>
       </c>
-      <c r="B20" t="s">
-        <v>216</v>
-      </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" t="s">
         <v>217</v>
-      </c>
-      <c r="B21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
         <v>219</v>
-      </c>
-      <c r="B22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" t="s">
         <v>221</v>
-      </c>
-      <c r="B23" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" t="s">
-        <v>222</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" t="s">
         <v>223</v>
-      </c>
-      <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>228</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
         <v>229</v>
-      </c>
-      <c r="B29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" t="s">
         <v>231</v>
       </c>
-      <c r="B30" t="s">
-        <v>232</v>
-      </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" t="s">
         <v>233</v>
-      </c>
-      <c r="B31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" t="s">
-        <v>234</v>
       </c>
       <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s">
         <v>235</v>
-      </c>
-      <c r="B32" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" t="s">
         <v>237</v>
-      </c>
-      <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>238</v>
+      </c>
+      <c r="B35" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" t="s">
         <v>239</v>
-      </c>
-      <c r="B35" t="s">
-        <v>154</v>
-      </c>
-      <c r="C35" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>261</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -2623,6 +2642,49 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925C6833-205D-497F-B2F5-6A5461A2AC6F}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2633,112 +2695,112 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C2F6B-401E-4411-BBF5-6C069DEFED2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74390C8F-33B5-4EAE-A17E-FF38DE8CB50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="312">
   <si>
     <t>Knight</t>
   </si>
@@ -413,9 +413,6 @@
     <t>Evolutions</t>
   </si>
   <si>
-    <t>POI Graphics &amp; Abilites &amp; Fade Text upon entering</t>
-  </si>
-  <si>
     <t>Cleanup unused code fragments</t>
   </si>
   <si>
@@ -941,25 +938,34 @@
     <t xml:space="preserve">Community Challenges– Every weekend, the developer picks a specific "Seed" and "Mode Combination." Everyone competes on a global leaderboard </t>
   </si>
   <si>
-    <t>1. Forest</t>
-  </si>
-  <si>
-    <t>2. Mountains</t>
-  </si>
-  <si>
-    <t>3. Volcano</t>
-  </si>
-  <si>
-    <t>4. River</t>
-  </si>
-  <si>
-    <t>5. Swamp</t>
-  </si>
-  <si>
-    <t>6. Plains</t>
-  </si>
-  <si>
     <t>Jungle</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Mountains</t>
+  </si>
+  <si>
+    <t>Volcano</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>Swamp</t>
+  </si>
+  <si>
+    <t>Plains</t>
+  </si>
+  <si>
+    <t>High Visibility Mode</t>
+  </si>
+  <si>
+    <t>POI Abilites &amp; Ability Fade Text upon entering</t>
+  </si>
+  <si>
+    <t>POI Graphics &amp; Fade Text upon entering</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1063,6 +1069,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1343,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1370,33 +1380,38 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>127</v>
+      <c r="A5" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>128</v>
+      <c r="A6" s="11" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>272</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1937,7 +1952,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2007,7 +2022,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2061,36 +2076,36 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
         <v>182</v>
-      </c>
-      <c r="B2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" t="s">
-        <v>183</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
         <v>184</v>
-      </c>
-      <c r="B3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" t="s">
-        <v>185</v>
       </c>
       <c r="D3" s="7"/>
     </row>
@@ -2099,540 +2114,542 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" t="s">
         <v>187</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>188</v>
-      </c>
-      <c r="C6" t="s">
-        <v>189</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" t="s">
         <v>191</v>
-      </c>
-      <c r="B8" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" t="s">
-        <v>192</v>
       </c>
       <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" t="s">
         <v>193</v>
-      </c>
-      <c r="B9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
         <v>195</v>
       </c>
-      <c r="B10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" t="s">
-        <v>196</v>
-      </c>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" t="s">
         <v>197</v>
-      </c>
-      <c r="B11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
         <v>202</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>203</v>
       </c>
-      <c r="C14" t="s">
-        <v>204</v>
-      </c>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" t="s">
         <v>206</v>
-      </c>
-      <c r="B16" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" t="s">
         <v>208</v>
-      </c>
-      <c r="B17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" t="s">
         <v>210</v>
-      </c>
-      <c r="B18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" t="s">
-        <v>211</v>
       </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" t="s">
         <v>212</v>
-      </c>
-      <c r="B19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s">
         <v>214</v>
       </c>
-      <c r="B20" t="s">
-        <v>215</v>
-      </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" t="s">
         <v>216</v>
-      </c>
-      <c r="B21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" t="s">
         <v>218</v>
-      </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s">
         <v>220</v>
-      </c>
-      <c r="B23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" t="s">
-        <v>221</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" t="s">
         <v>222</v>
-      </c>
-      <c r="B24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>227</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" t="s">
         <v>228</v>
-      </c>
-      <c r="B29" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
         <v>230</v>
       </c>
-      <c r="B30" t="s">
-        <v>231</v>
-      </c>
       <c r="C30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" t="s">
         <v>232</v>
-      </c>
-      <c r="B31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" t="s">
-        <v>233</v>
       </c>
       <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" t="s">
         <v>234</v>
-      </c>
-      <c r="B32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" t="s">
         <v>236</v>
-      </c>
-      <c r="B34" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
         <v>238</v>
-      </c>
-      <c r="B35" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>273</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>276</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -2650,32 +2667,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>308</v>
       </c>
     </row>
@@ -2686,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.21875" style="9" customWidth="1"/>
@@ -2695,112 +2712,117 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74390C8F-33B5-4EAE-A17E-FF38DE8CB50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A83667-A596-4D42-AAEF-0DD7CEE15A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,9 @@
     <sheet name="Enemies" sheetId="6" r:id="rId2"/>
     <sheet name="POI" sheetId="9" r:id="rId3"/>
     <sheet name="Weapons Audit" sheetId="8" r:id="rId4"/>
-    <sheet name="Biomes" sheetId="11" r:id="rId5"/>
-    <sheet name="Ideas" sheetId="10" r:id="rId6"/>
+    <sheet name="Ultimates" sheetId="12" r:id="rId5"/>
+    <sheet name="Biomes" sheetId="11" r:id="rId6"/>
+    <sheet name="Ideas" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="313">
   <si>
     <t>Knight</t>
   </si>
@@ -966,6 +967,9 @@
   </si>
   <si>
     <t>POI Graphics &amp; Fade Text upon entering</t>
+  </si>
+  <si>
+    <t>Cannonball</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1072,7 +1076,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1385,7 +1388,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="1" t="s">
         <v>310</v>
       </c>
     </row>
@@ -2086,410 +2089,412 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>182</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>184</v>
       </c>
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="7" t="s">
         <v>131</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>191</v>
       </c>
       <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>193</v>
       </c>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>254</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="7" t="s">
         <v>203</v>
       </c>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>210</v>
       </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>220</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>168</v>
       </c>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>255</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>230</v>
       </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>232</v>
       </c>
       <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>225</v>
+      <c r="C33" s="7" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="7" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>256</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="7" t="s">
         <v>154</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -2497,158 +2502,158 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="7" t="s">
         <v>164</v>
       </c>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="7" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="7" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="7" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="7" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="7" t="s">
         <v>278</v>
       </c>
     </row>
@@ -2659,6 +2664,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2393C09D-E45C-4F95-B0B3-4CD0B9B1A29F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925C6833-205D-497F-B2F5-6A5461A2AC6F}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2701,7 +2715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A83667-A596-4D42-AAEF-0DD7CEE15A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7968B4-477C-45AD-8605-22BF94CD0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Biomes" sheetId="11" r:id="rId6"/>
     <sheet name="Ideas" sheetId="10" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="332">
   <si>
     <t>Knight</t>
   </si>
@@ -828,12 +828,6 @@
     <t>Aeromancer</t>
   </si>
   <si>
-    <t>Meteor Smash</t>
-  </si>
-  <si>
-    <t>MeteorSmash</t>
-  </si>
-  <si>
     <t>Wind Storm</t>
   </si>
   <si>
@@ -970,6 +964,96 @@
   </si>
   <si>
     <t>Cannonball</t>
+  </si>
+  <si>
+    <t>Meteor Strike</t>
+  </si>
+  <si>
+    <t>MeteorStrike</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>RaritySort</t>
+  </si>
+  <si>
+    <t>*Character &amp; Weapon Unlock %
+Common - 53.125%
+Uncommon - 25%
+Rare - 12.5%
+Legendary - 6.25%
+Unique - 3.125%
+If all charaters at a given level are unlocked, that level's % is absorbed by the next highest level</t>
+  </si>
+  <si>
+    <t>Weapons unlock when the character is unlocked</t>
+  </si>
+  <si>
+    <t>Character Unlock code</t>
+  </si>
+  <si>
+    <t>Select 5 starting characters</t>
+  </si>
+  <si>
+    <t>Passive Items</t>
+  </si>
+  <si>
+    <t>Weapon Card availability
+Common - 53.125%
+Uncommon - 25%
+Rare - 12.5%
+Legendary - 6.25%
+Unique - 3.125%
+If all unlocked weapons at a given level are unlocked, that level's % is absorbed by the next highest level</t>
+  </si>
+  <si>
+    <t>Freestyle mode - customize weapons, enemies, etc.</t>
+  </si>
+  <si>
+    <t>Functionality</t>
+  </si>
+  <si>
+    <t>Weapon Card glow in the select menu, based on rarity (Blue, Green, Gold, Orange)</t>
+  </si>
+  <si>
+    <t>Elite Gold Border Sprite, Boss Orange Border Sprite, Unique Purple Border Sprite</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Weapon combination system where one weapon's sprite is used and the attack logic of the 2nd weapon is used (Allows for A + B or B + A)</t>
+  </si>
+  <si>
+    <t>Enhancement system where weapons can be upgraded further with elemental damage or physical characteristics
+Poison - every 1s for 3s deal 50% damage
+Burning - every 0.5s deal 0.85% of HP
+Vampiric - on hit, heal 10%
+Stunned - Reduce movement on hit to 0 for 1 seconds
+Slowed - Reduce movement on hit by 25% for 3 seconds
+Frozen - Reduce movement on hit by 10% for 5 seconds. If enemy has 100% reduction of movement from Frozen, play shatter animation on enemy, deal the lesser of 10% of hp or 10 damage and remove Frozen. 
+Electric - On hit, deal electric damage in a radius around enemy
+Magmatic - On hit, spawn an area of lava that deals damage each second for 10 seconds then despawns
+Gravitonian - Pulls enemies closer to the sprite 
+Bleeding - on hit, enemy loses 0.25% of health per second for 10 seconds.
+Blinding - on hit, enemy has a 50% chance to miss attacks and deal 0 damage and no attack effects for 3 seconds
+Increase Attack Speed by X
+Increase Damage by X
+(Unique) Increase number of attacks when referenced by a weapon by X
+(Unique) Increase the number of projectiles when referenced by a weapon by X</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1092,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,6 +1123,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1052,7 +1142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1075,6 +1165,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1356,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1384,12 +1478,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -1409,12 +1503,32 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2025,7 +2139,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2065,16 +2179,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134B62F-E2D3-4D00-ACEE-B088AA598477}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2085,579 +2200,951 @@
         <v>180</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F33" si="0">IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,""))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" t="s">
+        <v>317</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" t="s">
+        <v>317</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" t="s">
+        <v>317</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" t="s">
+        <v>317</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>317</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" t="s">
+        <v>317</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" t="s">
+        <v>317</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ref="F34:F65" si="1">IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,""))))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E35" t="s">
+        <v>317</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" t="s">
+        <v>317</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" t="s">
+        <v>317</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="C39" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" t="s">
+        <v>316</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" t="s">
+        <v>316</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" t="s">
+        <v>316</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E43" t="s">
+        <v>316</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" s="7"/>
+      <c r="E45" t="s">
+        <v>316</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E46" t="s">
+        <v>315</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" t="s">
+        <v>315</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" t="s">
+        <v>315</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B50" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D31" s="7"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36" s="7"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="E50" t="s">
+        <v>315</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D45" s="7"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>278</v>
+      <c r="E51" t="s">
+        <v>315</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F52">
+    <sortCondition ref="F2:F52"/>
+    <sortCondition ref="A2:A52"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2665,9 +3152,630 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2393C09D-E45C-4F95-B0B3-4CD0B9B1A29F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="150.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C33" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,""))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" t="s">
+        <v>314</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" t="s">
+        <v>317</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" t="s">
+        <v>317</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" t="s">
+        <v>317</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" t="s">
+        <v>317</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:C65" si="1">IF(B34="Common",1,IF(B34="Uncommon",2,IF(B34="Rare",3,IF(B34="Legendary",4,""))))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" t="s">
+        <v>317</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" t="s">
+        <v>317</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" t="s">
+        <v>316</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>190</v>
+      </c>
+      <c r="B42" t="s">
+        <v>316</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" t="s">
+        <v>316</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" t="s">
+        <v>316</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" t="s">
+        <v>315</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B47" t="s">
+        <v>315</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" t="s">
+        <v>315</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" t="s">
+        <v>315</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2682,32 +3790,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2717,126 +3825,156 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.21875" style="9" customWidth="1"/>
     <col min="2" max="2" width="38.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>129</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B5" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7968B4-477C-45AD-8605-22BF94CD0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE1C9DC-DDBF-41AD-9CC9-C8B02D5B9E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -459,9 +459,6 @@
     <t>Chain Lightning</t>
   </si>
   <si>
-    <t>Holy Staff</t>
-  </si>
-  <si>
     <t>Ice Shard</t>
   </si>
   <si>
@@ -679,9 +676,6 @@
   </si>
   <si>
     <t>Cleric</t>
-  </si>
-  <si>
-    <t>HolyStaff</t>
   </si>
   <si>
     <t>Cryomancer</t>
@@ -1003,9 +997,6 @@
   </si>
   <si>
     <t>Character Unlock code</t>
-  </si>
-  <si>
-    <t>Select 5 starting characters</t>
   </si>
   <si>
     <t>Passive Items</t>
@@ -1054,6 +1045,15 @@
 Increase Damage by X
 (Unique) Increase number of attacks when referenced by a weapon by X
 (Unique) Increase the number of projectiles when referenced by a weapon by X</t>
+  </si>
+  <si>
+    <t>Select 5 starting characters (Bold border in Wepons Audit)</t>
+  </si>
+  <si>
+    <t>Unique</t>
+  </si>
+  <si>
+    <t>ConversionZone</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1138,11 +1138,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1169,6 +1184,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1478,12 +1498,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -1503,32 +1523,32 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>322</v>
+      <c r="A14" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2069,7 +2089,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2139,7 +2159,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2194,117 +2214,117 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:F33" si="0">IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,""))))</f>
+        <f>IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,IF(E2="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f>IF(E3="Common",1,IF(E3="Uncommon",2,IF(E3="Rare",3,IF(E3="Legendary",4,IF(E3="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f>IF(E4="Common",1,IF(E4="Uncommon",2,IF(E4="Rare",3,IF(E4="Legendary",4,IF(E4="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <f>IF(E5="Common",1,IF(E5="Uncommon",2,IF(E5="Rare",3,IF(E5="Legendary",4,IF(E5="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>198</v>
+        <f>IF(E6="Common",1,IF(E6="Uncommon",2,IF(E6="Rare",3,IF(E6="Legendary",4,IF(E6="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>132</v>
@@ -2313,837 +2333,842 @@
         <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f>IF(E7="Common",1,IF(E7="Uncommon",2,IF(E7="Rare",3,IF(E7="Legendary",4,IF(E7="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f>IF(E8="Common",1,IF(E8="Uncommon",2,IF(E8="Rare",3,IF(E8="Legendary",4,IF(E8="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f>IF(E9="Common",1,IF(E9="Uncommon",2,IF(E9="Rare",3,IF(E9="Legendary",4,IF(E9="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="11"/>
+        <v>162</v>
+      </c>
       <c r="E10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f>IF(E10="Common",1,IF(E10="Uncommon",2,IF(E10="Rare",3,IF(E10="Legendary",4,IF(E10="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>163</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D11" s="7"/>
       <c r="E11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>0</v>
+        <f>IF(E11="Common",1,IF(E11="Uncommon",2,IF(E11="Rare",3,IF(E11="Legendary",4,IF(E11="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>180</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>181</v>
+        <f>IF(E12="Common",1,IF(E12="Uncommon",2,IF(E12="Rare",3,IF(E12="Legendary",4,IF(E12="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>208</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f>IF(E13="Common",1,IF(E13="Uncommon",2,IF(E13="Rare",3,IF(E13="Legendary",4,IF(E13="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>229</v>
+        <f>IF(E14="Common",1,IF(E14="Uncommon",2,IF(E14="Rare",3,IF(E14="Legendary",4,IF(E14="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>170</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D15" s="7"/>
+        <v>158</v>
+      </c>
+      <c r="D15" s="11"/>
       <c r="E15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>171</v>
+        <f>IF(E15="Common",1,IF(E15="Uncommon",2,IF(E15="Rare",3,IF(E15="Legendary",4,IF(E15="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>159</v>
+        <v>248</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>159</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D16" s="7"/>
       <c r="E16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>185</v>
+        <f>IF(E16="Common",1,IF(E16="Uncommon",2,IF(E16="Rare",3,IF(E16="Legendary",4,IF(E16="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>183</v>
+        <f>IF(E17="Common",1,IF(E17="Uncommon",2,IF(E17="Rare",3,IF(E17="Legendary",4,IF(E17="Unique",5,"")))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F18">
-        <f t="shared" si="0"/>
+        <f>IF(E18="Common",1,IF(E18="Uncommon",2,IF(E18="Rare",3,IF(E18="Legendary",4,IF(E18="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F19">
-        <f t="shared" si="0"/>
+        <f>IF(E19="Common",1,IF(E19="Uncommon",2,IF(E19="Rare",3,IF(E19="Legendary",4,IF(E19="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="7"/>
+        <v>167</v>
+      </c>
+      <c r="D20" s="11"/>
       <c r="E20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F20">
-        <f t="shared" si="0"/>
+        <f>IF(E20="Common",1,IF(E20="Uncommon",2,IF(E20="Rare",3,IF(E20="Legendary",4,IF(E20="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
+        <f>IF(E21="Common",1,IF(E21="Uncommon",2,IF(E21="Rare",3,IF(E21="Legendary",4,IF(E21="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(E22="Common",1,IF(E22="Uncommon",2,IF(E22="Rare",3,IF(E22="Legendary",4,IF(E22="Unique",5,"")))))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>264</v>
+        <v>193</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D23" s="11"/>
+        <v>194</v>
+      </c>
+      <c r="D23" s="7"/>
       <c r="E23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F23">
-        <f t="shared" si="0"/>
+        <f>IF(E23="Common",1,IF(E23="Uncommon",2,IF(E23="Rare",3,IF(E23="Legendary",4,IF(E23="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F24">
-        <f t="shared" si="0"/>
+        <f>IF(E24="Common",1,IF(E24="Uncommon",2,IF(E24="Rare",3,IF(E24="Legendary",4,IF(E24="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D25" s="7"/>
+        <v>216</v>
+      </c>
       <c r="E25" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F25">
-        <f t="shared" si="0"/>
+        <f>IF(E25="Common",1,IF(E25="Uncommon",2,IF(E25="Rare",3,IF(E25="Legendary",4,IF(E25="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F26">
-        <f t="shared" si="0"/>
+        <f>IF(E26="Common",1,IF(E26="Uncommon",2,IF(E26="Rare",3,IF(E26="Legendary",4,IF(E26="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>143</v>
+        <v>243</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F27">
-        <f t="shared" si="0"/>
+        <f>IF(E27="Common",1,IF(E27="Uncommon",2,IF(E27="Rare",3,IF(E27="Legendary",4,IF(E27="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>200</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="D28" s="7"/>
       <c r="E28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F28">
-        <f t="shared" si="0"/>
+        <f>IF(E28="Common",1,IF(E28="Uncommon",2,IF(E28="Rare",3,IF(E28="Legendary",4,IF(E28="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>245</v>
+        <v>144</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>212</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="D29" s="11"/>
       <c r="E29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F29">
-        <f t="shared" si="0"/>
+        <f>IF(E29="Common",1,IF(E29="Uncommon",2,IF(E29="Rare",3,IF(E29="Legendary",4,IF(E29="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>254</v>
+        <v>163</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F30">
-        <f t="shared" si="0"/>
+        <f>IF(E30="Common",1,IF(E30="Uncommon",2,IF(E30="Rare",3,IF(E30="Legendary",4,IF(E30="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D31" s="7"/>
+        <v>236</v>
+      </c>
       <c r="E31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
+        <f>IF(E31="Common",1,IF(E31="Uncommon",2,IF(E31="Rare",3,IF(E31="Legendary",4,IF(E31="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F32">
-        <f t="shared" si="0"/>
+        <f>IF(E32="Common",1,IF(E32="Uncommon",2,IF(E32="Rare",3,IF(E32="Legendary",4,IF(E32="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="D33" s="7"/>
       <c r="E33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F33">
-        <f t="shared" si="0"/>
+        <f>IF(E33="Common",1,IF(E33="Uncommon",2,IF(E33="Rare",3,IF(E33="Legendary",4,IF(E33="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D34" s="7"/>
+        <v>232</v>
+      </c>
+      <c r="D34" s="11"/>
       <c r="E34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:F65" si="1">IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,""))))</f>
+        <f>IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,IF(E34="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>234</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="D35" s="11"/>
       <c r="E35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F35">
-        <f t="shared" si="1"/>
+        <f>IF(E35="Common",1,IF(E35="Uncommon",2,IF(E35="Rare",3,IF(E35="Legendary",4,IF(E35="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D36" s="11"/>
+        <v>253</v>
+      </c>
+      <c r="D36" s="7"/>
       <c r="E36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F36">
-        <f t="shared" si="1"/>
+        <f>IF(E36="Common",1,IF(E36="Uncommon",2,IF(E36="Rare",3,IF(E36="Legendary",4,IF(E36="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D37" s="7"/>
+        <v>205</v>
+      </c>
+      <c r="D37" s="11"/>
       <c r="E37" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F37">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>IF(E37="Common",1,IF(E37="Uncommon",2,IF(E37="Rare",3,IF(E37="Legendary",4,IF(E37="Unique",5,"")))))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D38" s="11"/>
+        <v>271</v>
+      </c>
       <c r="E38" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F38">
-        <f t="shared" si="1"/>
+        <f>IF(E38="Common",1,IF(E38="Uncommon",2,IF(E38="Rare",3,IF(E38="Legendary",4,IF(E38="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>273</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="D39" s="11"/>
       <c r="E39" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F39">
-        <f t="shared" si="1"/>
+        <f>IF(E39="Common",1,IF(E39="Uncommon",2,IF(E39="Rare",3,IF(E39="Legendary",4,IF(E39="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>157</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D40" s="11"/>
       <c r="E40" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F40">
-        <f t="shared" si="1"/>
+        <f>IF(E40="Common",1,IF(E40="Uncommon",2,IF(E40="Rare",3,IF(E40="Legendary",4,IF(E40="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D41" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="D41" s="7"/>
       <c r="E41" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F41">
-        <f t="shared" si="1"/>
+        <f>IF(E41="Common",1,IF(E41="Uncommon",2,IF(E41="Rare",3,IF(E41="Legendary",4,IF(E41="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D42" s="7"/>
+        <v>257</v>
+      </c>
+      <c r="D42" s="11"/>
       <c r="E42" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F42">
-        <f t="shared" si="1"/>
+        <f>IF(E42="Common",1,IF(E42="Uncommon",2,IF(E42="Rare",3,IF(E42="Legendary",4,IF(E42="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>259</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="D43" s="7"/>
       <c r="E43" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F43">
-        <f t="shared" si="1"/>
+        <f>IF(E43="Common",1,IF(E43="Uncommon",2,IF(E43="Rare",3,IF(E43="Legendary",4,IF(E43="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F44">
-        <f t="shared" si="1"/>
+        <f>IF(E44="Common",1,IF(E44="Uncommon",2,IF(E44="Rare",3,IF(E44="Legendary",4,IF(E44="Unique",5,"")))))</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" s="7"/>
+        <v>265</v>
+      </c>
       <c r="E45" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F45">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>IF(E45="Common",1,IF(E45="Uncommon",2,IF(E45="Rare",3,IF(E45="Legendary",4,IF(E45="Unique",5,"")))))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>224</v>
+        <v>309</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>267</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="D46" s="11"/>
       <c r="E46" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F46">
-        <f t="shared" si="1"/>
+        <f>IF(E46="Common",1,IF(E46="Uncommon",2,IF(E46="Rare",3,IF(E46="Legendary",4,IF(E46="Unique",5,"")))))</f>
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F47">
-        <f t="shared" si="1"/>
+        <f>IF(E47="Common",1,IF(E47="Uncommon",2,IF(E47="Rare",3,IF(E47="Legendary",4,IF(E47="Unique",5,"")))))</f>
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F48">
-        <f t="shared" si="1"/>
+        <f>IF(E48="Common",1,IF(E48="Uncommon",2,IF(E48="Rare",3,IF(E48="Legendary",4,IF(E48="Unique",5,"")))))</f>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="F49">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>IF(E49="Common",1,IF(E49="Uncommon",2,IF(E49="Rare",3,IF(E49="Legendary",4,IF(E49="Unique",5,"")))))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="F50">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>IF(E50="Common",1,IF(E50="Uncommon",2,IF(E50="Rare",3,IF(E50="Legendary",4,IF(E50="Unique",5,"")))))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E51" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="F51">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>IF(E51="Common",1,IF(E51="Uncommon",2,IF(E51="Rare",3,IF(E51="Legendary",4,IF(E51="Unique",5,"")))))</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F52">
-    <sortCondition ref="F2:F52"/>
-    <sortCondition ref="A2:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F51">
+    <sortCondition ref="F2:F51"/>
+    <sortCondition ref="A2:A51"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3166,21 +3191,21 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C2">
         <f t="shared" ref="C2:C33" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,""))))</f>
@@ -3189,10 +3214,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C3">
         <f t="shared" si="0"/>
@@ -3201,10 +3226,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
@@ -3213,10 +3238,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
@@ -3225,10 +3250,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3237,10 +3262,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3249,10 +3274,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3261,10 +3286,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -3273,10 +3298,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -3285,10 +3310,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -3300,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -3309,10 +3334,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -3321,10 +3346,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -3333,10 +3358,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -3345,10 +3370,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -3357,10 +3382,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -3369,10 +3394,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -3381,10 +3406,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -3393,10 +3418,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -3405,10 +3430,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -3417,10 +3442,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -3429,10 +3454,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -3441,10 +3466,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -3453,10 +3478,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -3465,10 +3490,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -3477,10 +3502,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -3489,10 +3514,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -3501,10 +3526,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -3513,10 +3538,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -3525,10 +3550,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -3537,10 +3562,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -3549,10 +3574,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -3561,22 +3586,22 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C34">
-        <f t="shared" ref="C34:C65" si="1">IF(B34="Common",1,IF(B34="Uncommon",2,IF(B34="Rare",3,IF(B34="Legendary",4,""))))</f>
+        <f t="shared" ref="C34:C51" si="1">IF(B34="Common",1,IF(B34="Uncommon",2,IF(B34="Rare",3,IF(B34="Legendary",4,""))))</f>
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
@@ -3585,10 +3610,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
@@ -3597,10 +3622,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
@@ -3609,10 +3634,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
@@ -3621,10 +3646,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
@@ -3633,10 +3658,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
@@ -3645,10 +3670,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
@@ -3657,10 +3682,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
@@ -3669,10 +3694,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
@@ -3681,10 +3706,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
@@ -3693,10 +3718,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
@@ -3705,10 +3730,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
@@ -3717,10 +3742,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
@@ -3729,10 +3754,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B48" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
@@ -3741,10 +3766,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B49" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
@@ -3753,10 +3778,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
@@ -3765,10 +3790,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
@@ -3790,32 +3815,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3838,143 +3863,143 @@
         <v>129</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>297</v>
+        <v>280</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>295</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE1C9DC-DDBF-41AD-9CC9-C8B02D5B9E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF07B58-BE6F-4D23-9A3D-96DE892F1F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,11 @@
     <sheet name="Enemies" sheetId="6" r:id="rId2"/>
     <sheet name="POI" sheetId="9" r:id="rId3"/>
     <sheet name="Weapons Audit" sheetId="8" r:id="rId4"/>
-    <sheet name="Ultimates" sheetId="12" r:id="rId5"/>
-    <sheet name="Biomes" sheetId="11" r:id="rId6"/>
-    <sheet name="Ideas" sheetId="10" r:id="rId7"/>
+    <sheet name="Passive Items" sheetId="14" r:id="rId5"/>
+    <sheet name="Ultimates" sheetId="12" r:id="rId6"/>
+    <sheet name="Biomes" sheetId="11" r:id="rId7"/>
+    <sheet name="Ideas" sheetId="10" r:id="rId8"/>
+    <sheet name="Achievements" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="388">
   <si>
     <t>Knight</t>
   </si>
@@ -874,9 +876,6 @@
   </si>
   <si>
     <t>Temporal Echoes (The Time-Loop Mode) – The run is divided into short 2-minute loops that stack on top of each other. When the 2-minute timer hits zero, you are sent back to the start. However, a "Ghost Echo" of your previous run is now playing alongside you, performing the exact movements and shots you did in the last loop.</t>
-  </si>
-  <si>
-    <t>Shifting Biomes – The map is a grid of rooms that physically shift and rearrange every 60 seconds.</t>
   </si>
   <si>
     <t>Roulette Weapons – Every 2 minutes, your weapons randomly swaps to different ones</t>
@@ -1054,6 +1053,177 @@
   </si>
   <si>
     <t>ConversionZone</t>
+  </si>
+  <si>
+    <t>Easter Egg Achievements of find the D4/6/8/10/12/20/% (D&amp;D) Dice Sprites</t>
+  </si>
+  <si>
+    <t>Achievements</t>
+  </si>
+  <si>
+    <t>Beat Normal/Hard/Legendary on each map</t>
+  </si>
+  <si>
+    <t>Complete Campaign Mode</t>
+  </si>
+  <si>
+    <t>Unlock All characters</t>
+  </si>
+  <si>
+    <t>Beat a level using the Cleric</t>
+  </si>
+  <si>
+    <t>Beat a level using the Necromancer</t>
+  </si>
+  <si>
+    <t>Beat a level using the Puppetmaster</t>
+  </si>
+  <si>
+    <t>Nightmare Mode (2x Damage to enemies)</t>
+  </si>
+  <si>
+    <t>Beat Nightmare Mode Campaign</t>
+  </si>
+  <si>
+    <t>Unlock Sigil Architect Mode</t>
+  </si>
+  <si>
+    <t>Unlock Parasite Enemies Mode</t>
+  </si>
+  <si>
+    <t>Beat Parasite Enemies Mode</t>
+  </si>
+  <si>
+    <t>Beat Sigil Architect Mode</t>
+  </si>
+  <si>
+    <t>Unlock Auction House Mode</t>
+  </si>
+  <si>
+    <t>Beat Auction House Mode</t>
+  </si>
+  <si>
+    <t>Unlock Temporal Echoes Mode</t>
+  </si>
+  <si>
+    <t>Beat Temporal Echoes Mode</t>
+  </si>
+  <si>
+    <t>Labarinth – The map is a grid of rooms that physically shift and rearrange every 60 seconds.</t>
+  </si>
+  <si>
+    <t>Unlock Labarinth Mode</t>
+  </si>
+  <si>
+    <t>Beat Labarinth Mode</t>
+  </si>
+  <si>
+    <t>Unlock Roulette Mode</t>
+  </si>
+  <si>
+    <t>Beat Roulette Mode</t>
+  </si>
+  <si>
+    <t>Unlock Extraction Mode</t>
+  </si>
+  <si>
+    <t>Beat Extraction Mode</t>
+  </si>
+  <si>
+    <t>Unlock Shadow Mode</t>
+  </si>
+  <si>
+    <t>Beat Shadow Mode</t>
+  </si>
+  <si>
+    <t>Unlock Nightmare Mode (2x damage from enemies)</t>
+  </si>
+  <si>
+    <t>Unlock Shared Pool Mode</t>
+  </si>
+  <si>
+    <t>Win a game of Shared Pool Mode PVP</t>
+  </si>
+  <si>
+    <t>Win a game of Shared Pool Mode PVE</t>
+  </si>
+  <si>
+    <t>Unlock Through The Looking Glass Mode</t>
+  </si>
+  <si>
+    <t>Win a game of TTLG Mode as the player</t>
+  </si>
+  <si>
+    <t>Win a game of TTLG Mode as the enemies</t>
+  </si>
+  <si>
+    <t>Unlock Minimalist Mode</t>
+  </si>
+  <si>
+    <t>beat minimalist mode</t>
+  </si>
+  <si>
+    <t>Unlock Floor is lava mode</t>
+  </si>
+  <si>
+    <t>beat floor is lava mode</t>
+  </si>
+  <si>
+    <t>Unlock Boss Rush Mode</t>
+  </si>
+  <si>
+    <t>Beat Boss rush mode</t>
+  </si>
+  <si>
+    <t>Unlock Mode Fusion</t>
+  </si>
+  <si>
+    <t>Beat each fusion mode</t>
+  </si>
+  <si>
+    <t>Beat all fusion modes</t>
+  </si>
+  <si>
+    <t>Unlock freestyle mode</t>
+  </si>
+  <si>
+    <t>beat freestyle mode on any settings</t>
+  </si>
+  <si>
+    <t>beat freestyle mode on the hardest settings</t>
+  </si>
+  <si>
+    <t>Discover each type of enemy</t>
+  </si>
+  <si>
+    <t>Discover all enemies</t>
+  </si>
+  <si>
+    <t>Discover all elites</t>
+  </si>
+  <si>
+    <t>Discover all bosses</t>
+  </si>
+  <si>
+    <t>beat all enemy types</t>
+  </si>
+  <si>
+    <t>beat all elite types</t>
+  </si>
+  <si>
+    <t>beat all boss types</t>
+  </si>
+  <si>
+    <t>deal X damage (100k?)</t>
+  </si>
+  <si>
+    <t>Heal X hp (100k?)</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Ability</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1186,7 +1356,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1498,12 +1667,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -1533,22 +1702,22 @@
     </row>
     <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -2159,7 +2328,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2223,10 +2392,10 @@
         <v>268</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2241,10 +2410,10 @@
       </c>
       <c r="D2" s="7"/>
       <c r="E2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F2">
-        <f>IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,IF(E2="Unique",5,"")))))</f>
+        <f t="shared" ref="F2:F33" si="0">IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,IF(E2="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
@@ -2259,10 +2428,10 @@
         <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F3">
-        <f>IF(E3="Common",1,IF(E3="Uncommon",2,IF(E3="Rare",3,IF(E3="Legendary",4,IF(E3="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2278,10 +2447,10 @@
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F4">
-        <f>IF(E4="Common",1,IF(E4="Uncommon",2,IF(E4="Rare",3,IF(E4="Legendary",4,IF(E4="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2297,10 +2466,10 @@
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F5">
-        <f>IF(E5="Common",1,IF(E5="Uncommon",2,IF(E5="Rare",3,IF(E5="Legendary",4,IF(E5="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2315,10 +2484,10 @@
         <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F6">
-        <f>IF(E6="Common",1,IF(E6="Uncommon",2,IF(E6="Rare",3,IF(E6="Legendary",4,IF(E6="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2332,11 +2501,12 @@
       <c r="C7" s="7" t="s">
         <v>132</v>
       </c>
+      <c r="D7" s="11"/>
       <c r="E7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F7">
-        <f>IF(E7="Common",1,IF(E7="Uncommon",2,IF(E7="Rare",3,IF(E7="Legendary",4,IF(E7="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2351,10 +2521,10 @@
         <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F8">
-        <f>IF(E8="Common",1,IF(E8="Uncommon",2,IF(E8="Rare",3,IF(E8="Legendary",4,IF(E8="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2366,14 +2536,14 @@
         <v>149</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F9">
-        <f>IF(E9="Common",1,IF(E9="Uncommon",2,IF(E9="Rare",3,IF(E9="Legendary",4,IF(E9="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2387,11 +2557,12 @@
       <c r="C10" s="7" t="s">
         <v>162</v>
       </c>
+      <c r="D10" s="11"/>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F10">
-        <f>IF(E10="Common",1,IF(E10="Uncommon",2,IF(E10="Rare",3,IF(E10="Legendary",4,IF(E10="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2407,15 +2578,15 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F11">
-        <f>IF(E11="Common",1,IF(E11="Uncommon",2,IF(E11="Rare",3,IF(E11="Legendary",4,IF(E11="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="7" t="s">
         <v>180</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -2426,10 +2597,10 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F12">
-        <f>IF(E12="Common",1,IF(E12="Uncommon",2,IF(E12="Rare",3,IF(E12="Legendary",4,IF(E12="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2445,10 +2616,10 @@
       </c>
       <c r="D13" s="7"/>
       <c r="E13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F13">
-        <f>IF(E13="Common",1,IF(E13="Uncommon",2,IF(E13="Rare",3,IF(E13="Legendary",4,IF(E13="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2464,15 +2635,15 @@
       </c>
       <c r="D14" s="7"/>
       <c r="E14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F14">
-        <f>IF(E14="Common",1,IF(E14="Uncommon",2,IF(E14="Rare",3,IF(E14="Legendary",4,IF(E14="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>170</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -2483,10 +2654,10 @@
       </c>
       <c r="D15" s="11"/>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F15">
-        <f>IF(E15="Common",1,IF(E15="Uncommon",2,IF(E15="Rare",3,IF(E15="Legendary",4,IF(E15="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2502,10 +2673,10 @@
       </c>
       <c r="D16" s="7"/>
       <c r="E16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F16">
-        <f>IF(E16="Common",1,IF(E16="Uncommon",2,IF(E16="Rare",3,IF(E16="Legendary",4,IF(E16="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2521,10 +2692,10 @@
       </c>
       <c r="D17" s="7"/>
       <c r="E17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F17">
-        <f>IF(E17="Common",1,IF(E17="Uncommon",2,IF(E17="Rare",3,IF(E17="Legendary",4,IF(E17="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2540,10 +2711,10 @@
       </c>
       <c r="D18" s="7"/>
       <c r="E18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F18">
-        <f>IF(E18="Common",1,IF(E18="Uncommon",2,IF(E18="Rare",3,IF(E18="Legendary",4,IF(E18="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2559,10 +2730,10 @@
       </c>
       <c r="D19" s="7"/>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F19">
-        <f>IF(E19="Common",1,IF(E19="Uncommon",2,IF(E19="Rare",3,IF(E19="Legendary",4,IF(E19="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2578,10 +2749,10 @@
       </c>
       <c r="D20" s="11"/>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F20">
-        <f>IF(E20="Common",1,IF(E20="Uncommon",2,IF(E20="Rare",3,IF(E20="Legendary",4,IF(E20="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2597,10 +2768,10 @@
       </c>
       <c r="D21" s="11"/>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F21">
-        <f>IF(E21="Common",1,IF(E21="Uncommon",2,IF(E21="Rare",3,IF(E21="Legendary",4,IF(E21="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2616,10 +2787,10 @@
       </c>
       <c r="D22" s="11"/>
       <c r="E22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F22">
-        <f>IF(E22="Common",1,IF(E22="Uncommon",2,IF(E22="Rare",3,IF(E22="Legendary",4,IF(E22="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2635,10 +2806,10 @@
       </c>
       <c r="D23" s="7"/>
       <c r="E23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F23">
-        <f>IF(E23="Common",1,IF(E23="Uncommon",2,IF(E23="Rare",3,IF(E23="Legendary",4,IF(E23="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2654,10 +2825,10 @@
       </c>
       <c r="D24" s="7"/>
       <c r="E24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F24">
-        <f>IF(E24="Common",1,IF(E24="Uncommon",2,IF(E24="Rare",3,IF(E24="Legendary",4,IF(E24="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2672,10 +2843,10 @@
         <v>216</v>
       </c>
       <c r="E25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F25">
-        <f>IF(E25="Common",1,IF(E25="Uncommon",2,IF(E25="Rare",3,IF(E25="Legendary",4,IF(E25="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2690,10 +2861,10 @@
         <v>199</v>
       </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F26">
-        <f>IF(E26="Common",1,IF(E26="Uncommon",2,IF(E26="Rare",3,IF(E26="Legendary",4,IF(E26="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2707,11 +2878,12 @@
       <c r="C27" s="7" t="s">
         <v>211</v>
       </c>
+      <c r="D27" s="11"/>
       <c r="E27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F27">
-        <f>IF(E27="Common",1,IF(E27="Uncommon",2,IF(E27="Rare",3,IF(E27="Legendary",4,IF(E27="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2727,10 +2899,10 @@
       </c>
       <c r="D28" s="7"/>
       <c r="E28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F28">
-        <f>IF(E28="Common",1,IF(E28="Uncommon",2,IF(E28="Rare",3,IF(E28="Legendary",4,IF(E28="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2746,10 +2918,10 @@
       </c>
       <c r="D29" s="11"/>
       <c r="E29" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F29">
-        <f>IF(E29="Common",1,IF(E29="Uncommon",2,IF(E29="Rare",3,IF(E29="Legendary",4,IF(E29="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2765,10 +2937,10 @@
       </c>
       <c r="D30" s="7"/>
       <c r="E30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F30">
-        <f>IF(E30="Common",1,IF(E30="Uncommon",2,IF(E30="Rare",3,IF(E30="Legendary",4,IF(E30="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2783,10 +2955,10 @@
         <v>236</v>
       </c>
       <c r="E31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F31">
-        <f>IF(E31="Common",1,IF(E31="Uncommon",2,IF(E31="Rare",3,IF(E31="Legendary",4,IF(E31="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2801,10 +2973,10 @@
         <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F32">
-        <f>IF(E32="Common",1,IF(E32="Uncommon",2,IF(E32="Rare",3,IF(E32="Legendary",4,IF(E32="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2820,10 +2992,10 @@
       </c>
       <c r="D33" s="7"/>
       <c r="E33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F33">
-        <f>IF(E33="Common",1,IF(E33="Uncommon",2,IF(E33="Rare",3,IF(E33="Legendary",4,IF(E33="Unique",5,"")))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2839,10 +3011,10 @@
       </c>
       <c r="D34" s="11"/>
       <c r="E34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F34">
-        <f>IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,IF(E34="Unique",5,"")))))</f>
+        <f t="shared" ref="F34:F51" si="1">IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,IF(E34="Unique",5,"")))))</f>
         <v>2</v>
       </c>
     </row>
@@ -2858,10 +3030,10 @@
       </c>
       <c r="D35" s="11"/>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F35">
-        <f>IF(E35="Common",1,IF(E35="Uncommon",2,IF(E35="Rare",3,IF(E35="Legendary",4,IF(E35="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2877,10 +3049,10 @@
       </c>
       <c r="D36" s="7"/>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F36">
-        <f>IF(E36="Common",1,IF(E36="Uncommon",2,IF(E36="Rare",3,IF(E36="Legendary",4,IF(E36="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2896,10 +3068,10 @@
       </c>
       <c r="D37" s="11"/>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F37">
-        <f>IF(E37="Common",1,IF(E37="Uncommon",2,IF(E37="Rare",3,IF(E37="Legendary",4,IF(E37="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2914,10 +3086,10 @@
         <v>271</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F38">
-        <f>IF(E38="Common",1,IF(E38="Uncommon",2,IF(E38="Rare",3,IF(E38="Legendary",4,IF(E38="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2933,10 +3105,10 @@
       </c>
       <c r="D39" s="11"/>
       <c r="E39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F39">
-        <f>IF(E39="Common",1,IF(E39="Uncommon",2,IF(E39="Rare",3,IF(E39="Legendary",4,IF(E39="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2952,10 +3124,10 @@
       </c>
       <c r="D40" s="11"/>
       <c r="E40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F40">
-        <f>IF(E40="Common",1,IF(E40="Uncommon",2,IF(E40="Rare",3,IF(E40="Legendary",4,IF(E40="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2971,10 +3143,10 @@
       </c>
       <c r="D41" s="7"/>
       <c r="E41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F41">
-        <f>IF(E41="Common",1,IF(E41="Uncommon",2,IF(E41="Rare",3,IF(E41="Legendary",4,IF(E41="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2990,10 +3162,10 @@
       </c>
       <c r="D42" s="11"/>
       <c r="E42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F42">
-        <f>IF(E42="Common",1,IF(E42="Uncommon",2,IF(E42="Rare",3,IF(E42="Legendary",4,IF(E42="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -3009,10 +3181,10 @@
       </c>
       <c r="D43" s="7"/>
       <c r="E43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F43">
-        <f>IF(E43="Common",1,IF(E43="Uncommon",2,IF(E43="Rare",3,IF(E43="Legendary",4,IF(E43="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -3028,10 +3200,10 @@
       </c>
       <c r="D44" s="7"/>
       <c r="E44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F44">
-        <f>IF(E44="Common",1,IF(E44="Uncommon",2,IF(E44="Rare",3,IF(E44="Legendary",4,IF(E44="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -3046,10 +3218,10 @@
         <v>265</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F45">
-        <f>IF(E45="Common",1,IF(E45="Uncommon",2,IF(E45="Rare",3,IF(E45="Legendary",4,IF(E45="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -3058,17 +3230,17 @@
         <v>261</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F46">
-        <f>IF(E46="Common",1,IF(E46="Uncommon",2,IF(E46="Rare",3,IF(E46="Legendary",4,IF(E46="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -3084,10 +3256,10 @@
       </c>
       <c r="D47" s="11"/>
       <c r="E47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F47">
-        <f>IF(E47="Common",1,IF(E47="Uncommon",2,IF(E47="Rare",3,IF(E47="Legendary",4,IF(E47="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -3103,10 +3275,10 @@
       </c>
       <c r="D48" s="11"/>
       <c r="E48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F48">
-        <f>IF(E48="Common",1,IF(E48="Uncommon",2,IF(E48="Rare",3,IF(E48="Legendary",4,IF(E48="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -3115,17 +3287,17 @@
         <v>214</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F49">
-        <f>IF(E49="Common",1,IF(E49="Uncommon",2,IF(E49="Rare",3,IF(E49="Legendary",4,IF(E49="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -3140,10 +3312,10 @@
         <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F50">
-        <f>IF(E50="Common",1,IF(E50="Uncommon",2,IF(E50="Rare",3,IF(E50="Legendary",4,IF(E50="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -3158,10 +3330,10 @@
         <v>223</v>
       </c>
       <c r="E51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F51">
-        <f>IF(E51="Common",1,IF(E51="Uncommon",2,IF(E51="Rare",3,IF(E51="Legendary",4,IF(E51="Unique",5,"")))))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -3176,13 +3348,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADDDF46-43D1-4A7A-BD4D-3DE706CA4551}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2393C09D-E45C-4F95-B0B3-4CD0B9B1A29F}">
   <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="150.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3191,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3205,10 +3394,10 @@
         <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C33" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,""))))</f>
+        <f t="shared" ref="C2:C51" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,IF(B2="Unique",5,"")))))</f>
         <v>1</v>
       </c>
     </row>
@@ -3217,7 +3406,7 @@
         <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C3">
         <f t="shared" si="0"/>
@@ -3229,7 +3418,7 @@
         <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
@@ -3241,7 +3430,7 @@
         <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
@@ -3253,7 +3442,7 @@
         <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3265,7 +3454,7 @@
         <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3277,7 +3466,7 @@
         <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3286,10 +3475,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -3298,10 +3487,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -3310,10 +3499,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -3322,10 +3511,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -3334,10 +3523,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -3346,10 +3535,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -3358,10 +3547,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -3370,10 +3559,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -3382,10 +3571,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -3394,10 +3583,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -3406,10 +3595,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -3418,10 +3607,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -3430,10 +3619,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -3442,22 +3631,22 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -3466,10 +3655,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -3478,10 +3667,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -3490,10 +3679,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -3502,10 +3691,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -3514,10 +3703,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -3526,10 +3715,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -3538,10 +3727,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -3550,10 +3739,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -3562,10 +3751,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -3574,10 +3763,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -3586,194 +3775,194 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C34">
-        <f t="shared" ref="C34:C51" si="1">IF(B34="Common",1,IF(B34="Uncommon",2,IF(B34="Rare",3,IF(B34="Legendary",4,""))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="B35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C37">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="B42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C45">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>261</v>
       </c>
       <c r="B46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C49">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -3781,11 +3970,11 @@
         <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C50">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -3793,11 +3982,11 @@
         <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C51">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3805,7 +3994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925C6833-205D-497F-B2F5-6A5461A2AC6F}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3815,32 +4004,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -3848,9 +4037,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC19137E-1A1C-4137-828B-A034EA426793}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.21875" style="9" customWidth="1"/>
@@ -3866,7 +4055,7 @@
         <v>276</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
@@ -3877,18 +4066,18 @@
         <v>275</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>290</v>
+      <c r="B3" s="14" t="s">
+        <v>289</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
@@ -3896,114 +4085,397 @@
         <v>279</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>295</v>
+      <c r="B5" s="14" t="s">
+        <v>294</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5703EFDC-47D5-4A40-97CD-E1B5E5876EFD}">
+  <dimension ref="A1:A53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF07B58-BE6F-4D23-9A3D-96DE892F1F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E727D29-CA7C-4862-9717-712B59756EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="393">
   <si>
     <t>Knight</t>
   </si>
@@ -753,9 +753,6 @@
   </si>
   <si>
     <t>Saw Blade</t>
-  </si>
-  <si>
-    <t>Frost Bolt</t>
   </si>
   <si>
     <t>Tidal Wave</t>
@@ -1224,6 +1221,24 @@
   </si>
   <si>
     <t>Ability</t>
+  </si>
+  <si>
+    <t>Blizzard</t>
+  </si>
+  <si>
+    <t>The necromancer ultimate has a 75% chance to spawn a random elite of an enemy that has been killed this game. If no elites have been killed this game, spawn an elite creeper. Elites have double hp and damage as the regular versions, and move 25% faster. They also have a golden glow around their sprite. The necromancer has a 25% chance to spawn a random boss that has been killed this game. If no bosses have been killed this game, spawn a random elite enemy that has been killed instead. if no bosses or elites have been killed this game, spawn an elite creeper instead. Bosses have a red glow around their sprite.  The summoned charmed enemies are summoned at a random point in a circle around the player.</t>
+  </si>
+  <si>
+    <t>The Puppetmaster ultimate should summon 3 more shadowclones, all with their own behavior that mimics the existing shadow clone logic, but one to the south, north , and west of the player. The ultimate spawned shadowclones and their weapons are destroyed after 12 seconds</t>
+  </si>
+  <si>
+    <t>the Cleric ultimate should instantly convert 50% of the enemies on the screen. Elites have a 50% chance to be converted by this action. Bosses have a 10% chance.</t>
+  </si>
+  <si>
+    <t>Activate all Time Manipulation effects at once</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1277,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1278,12 +1293,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1327,22 +1336,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1351,12 +1359,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1639,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1667,12 +1675,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -1681,7 +1689,7 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1691,33 +1699,38 @@
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>267</v>
+      <c r="A10" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>317</v>
+      <c r="A12" s="8" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2271,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2328,7 +2341,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2389,28 +2402,28 @@
         <v>179</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" t="s">
         <v>310</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" t="s">
-        <v>311</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F33" si="0">IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,IF(E2="Unique",5,"")))))</f>
@@ -2418,600 +2431,607 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" t="s">
+        <v>310</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" t="s">
+        <v>310</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" t="s">
+        <v>310</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" t="s">
+        <v>310</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" t="s">
+        <v>310</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" t="s">
+        <v>310</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" t="s">
+        <v>310</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" t="s">
+        <v>310</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" t="s">
+        <v>313</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" t="s">
+        <v>313</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" t="s">
+        <v>313</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" t="s">
+        <v>313</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" t="s">
+        <v>313</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" t="s">
+        <v>313</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" t="s">
-        <v>311</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" t="s">
-        <v>311</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" t="s">
-        <v>311</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" t="s">
-        <v>311</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" t="s">
-        <v>311</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" t="s">
-        <v>311</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" t="s">
-        <v>311</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" t="s">
-        <v>311</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" t="s">
-        <v>311</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" t="s">
-        <v>314</v>
-      </c>
-      <c r="F22">
+      <c r="C30" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" t="s">
+        <v>313</v>
+      </c>
+      <c r="F31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" t="s">
-        <v>314</v>
-      </c>
-      <c r="F24">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E25" t="s">
-        <v>314</v>
-      </c>
-      <c r="F25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" t="s">
+        <v>313</v>
+      </c>
+      <c r="F33">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" t="s">
-        <v>314</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" t="s">
-        <v>314</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" t="s">
-        <v>314</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" t="s">
-        <v>314</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" t="s">
-        <v>314</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="E31" t="s">
-        <v>314</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E32" t="s">
-        <v>314</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" s="7"/>
-      <c r="E33" t="s">
-        <v>314</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D34" s="11"/>
+      <c r="D34" s="10"/>
       <c r="E34" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F34">
         <f t="shared" ref="F34:F51" si="1">IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,IF(E34="Unique",5,"")))))</f>
@@ -3019,18 +3039,18 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D35" s="11"/>
+      <c r="D35" s="10"/>
       <c r="E35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
@@ -3038,18 +3058,18 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="D36" s="7"/>
+      <c r="C36" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="6"/>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
@@ -3057,18 +3077,18 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C37" s="7" t="s">
+      <c r="B37" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D37" s="11"/>
+      <c r="D37" s="10"/>
       <c r="E37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F37">
         <f t="shared" si="1"/>
@@ -3076,17 +3096,18 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>271</v>
-      </c>
+      <c r="D38" s="10"/>
       <c r="E38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F38">
         <f t="shared" si="1"/>
@@ -3094,18 +3115,18 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="11"/>
+      <c r="D39" s="10"/>
       <c r="E39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
@@ -3113,18 +3134,18 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D40" s="11"/>
+      <c r="D40" s="10"/>
       <c r="E40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F40">
         <f t="shared" si="1"/>
@@ -3132,18 +3153,18 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C41" s="7" t="s">
+      <c r="B41" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D41" s="7"/>
+      <c r="D41" s="6"/>
       <c r="E41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F41">
         <f t="shared" si="1"/>
@@ -3151,18 +3172,18 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D42" s="11"/>
+      <c r="D42" s="10"/>
       <c r="E42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F42">
         <f t="shared" si="1"/>
@@ -3170,18 +3191,18 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="7"/>
+      <c r="D43" s="6"/>
       <c r="E43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
@@ -3189,18 +3210,18 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D44" s="7"/>
+      <c r="D44" s="6"/>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
@@ -3208,17 +3229,18 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>265</v>
-      </c>
+      <c r="C45" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="10"/>
       <c r="E45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
@@ -3226,18 +3248,18 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B46" s="7" t="s">
+      <c r="A46" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D46" s="11"/>
+      <c r="D46" s="10"/>
       <c r="E46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
@@ -3245,18 +3267,18 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" s="11"/>
+      <c r="D47" s="10"/>
       <c r="E47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
@@ -3264,18 +3286,18 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D48" s="11"/>
+      <c r="D48" s="10"/>
       <c r="E48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F48">
         <f t="shared" si="1"/>
@@ -3283,18 +3305,18 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="D49" s="11"/>
+      <c r="B49" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D49" s="10"/>
       <c r="E49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
@@ -3302,17 +3324,18 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>160</v>
       </c>
+      <c r="D50" s="10"/>
       <c r="E50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
@@ -3320,17 +3343,18 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="10" t="s">
         <v>223</v>
       </c>
+      <c r="D51" s="10"/>
       <c r="E51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F51">
         <f t="shared" si="1"/>
@@ -3354,10 +3378,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" t="s">
         <v>386</v>
-      </c>
-      <c r="B1" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -3372,7 +3396,7 @@
   <cols>
     <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="150.5546875" customWidth="1"/>
+    <col min="4" max="4" width="150.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3380,13 +3404,13 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3394,7 +3418,7 @@
         <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C2">
         <f t="shared" ref="C2:C51" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,IF(B2="Unique",5,"")))))</f>
@@ -3406,7 +3430,7 @@
         <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C3">
         <f t="shared" si="0"/>
@@ -3418,7 +3442,7 @@
         <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
@@ -3430,7 +3454,7 @@
         <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
@@ -3442,7 +3466,7 @@
         <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3454,7 +3478,7 @@
         <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3466,7 +3490,7 @@
         <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3478,7 +3502,7 @@
         <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -3490,7 +3514,7 @@
         <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -3502,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -3514,7 +3538,7 @@
         <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -3526,7 +3550,7 @@
         <v>208</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -3538,7 +3562,7 @@
         <v>227</v>
       </c>
       <c r="B14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -3550,7 +3574,7 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -3562,7 +3586,7 @@
         <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -3574,7 +3598,7 @@
         <v>182</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -3586,7 +3610,7 @@
         <v>185</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -3598,7 +3622,7 @@
         <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -3610,7 +3634,7 @@
         <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -3622,7 +3646,7 @@
         <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -3631,10 +3655,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -3646,7 +3670,7 @@
         <v>193</v>
       </c>
       <c r="B23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -3658,7 +3682,7 @@
         <v>175</v>
       </c>
       <c r="B24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -3670,7 +3694,7 @@
         <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -3682,7 +3706,7 @@
         <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -3694,7 +3718,7 @@
         <v>210</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -3706,7 +3730,7 @@
         <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -3718,7 +3742,7 @@
         <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -3730,7 +3754,7 @@
         <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -3742,7 +3766,7 @@
         <v>235</v>
       </c>
       <c r="B31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -3754,239 +3778,251 @@
         <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>206</v>
       </c>
       <c r="B35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>224</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>191</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C40">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C42">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>200</v>
       </c>
       <c r="B43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="8" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="8" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
         <v>5</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -4003,33 +4039,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4042,158 +4078,158 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="80.21875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.21875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.5546875" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="B2" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>321</v>
-      </c>
-    </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
-        <v>339</v>
+      <c r="A22" s="8" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4211,268 +4247,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>332</v>
+      <c r="A1" s="7" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E727D29-CA7C-4862-9717-712B59756EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2173BC6-923F-42EB-B62D-3EDD7AF99E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="392">
   <si>
     <t>Knight</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>Enemies</t>
-  </si>
-  <si>
-    <t>Sprites</t>
   </si>
   <si>
     <t>Ads</t>
@@ -1238,7 +1235,7 @@
     <t>Activate all Time Manipulation effects at once</t>
   </si>
   <si>
-    <t>c</t>
+    <t>Character &amp; Weapon Sprites</t>
   </si>
 </sst>
 </file>
@@ -1647,90 +1644,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7489455-9382-49C5-B393-E37B70D6D99A}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>123</v>
+      <c r="A1" s="3" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>392</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2341,7 +2333,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -2396,34 +2388,34 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F33" si="0">IF(E2="Common",1,IF(E2="Uncommon",2,IF(E2="Rare",3,IF(E2="Legendary",4,IF(E2="Unique",5,"")))))</f>
@@ -2432,17 +2424,17 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
@@ -2451,17 +2443,17 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
@@ -2470,17 +2462,17 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
@@ -2489,17 +2481,17 @@
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
@@ -2508,17 +2500,17 @@
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
@@ -2527,17 +2519,17 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
@@ -2546,17 +2538,17 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
@@ -2565,17 +2557,17 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
@@ -2587,14 +2579,14 @@
         <v>0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
@@ -2603,17 +2595,17 @@
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
@@ -2622,17 +2614,17 @@
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
@@ -2641,17 +2633,17 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="C14" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
@@ -2660,17 +2652,17 @@
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
@@ -2679,17 +2671,17 @@
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
@@ -2698,17 +2690,17 @@
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
@@ -2717,17 +2709,17 @@
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
@@ -2736,17 +2728,17 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
@@ -2755,17 +2747,17 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
@@ -2774,17 +2766,17 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F21">
         <f t="shared" si="0"/>
@@ -2793,17 +2785,17 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
@@ -2812,17 +2804,17 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
@@ -2831,17 +2823,17 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F24">
         <f t="shared" si="0"/>
@@ -2850,17 +2842,17 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
@@ -2869,17 +2861,17 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="C26" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F26">
         <f t="shared" si="0"/>
@@ -2888,17 +2880,17 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F27">
         <f t="shared" si="0"/>
@@ -2907,17 +2899,17 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F28">
         <f t="shared" si="0"/>
@@ -2926,17 +2918,17 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F29">
         <f t="shared" si="0"/>
@@ -2945,17 +2937,17 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
@@ -2964,17 +2956,17 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F31">
         <f t="shared" si="0"/>
@@ -2983,17 +2975,17 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F32">
         <f t="shared" si="0"/>
@@ -3002,17 +2994,17 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F33">
         <f t="shared" si="0"/>
@@ -3021,17 +3013,17 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F34">
         <f t="shared" ref="F34:F51" si="1">IF(E34="Common",1,IF(E34="Uncommon",2,IF(E34="Rare",3,IF(E34="Legendary",4,IF(E34="Unique",5,"")))))</f>
@@ -3040,17 +3032,17 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
@@ -3059,17 +3051,17 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
@@ -3078,17 +3070,17 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F37">
         <f t="shared" si="1"/>
@@ -3097,17 +3089,17 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F38">
         <f t="shared" si="1"/>
@@ -3116,17 +3108,17 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
@@ -3135,17 +3127,17 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F40">
         <f t="shared" si="1"/>
@@ -3154,17 +3146,17 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F41">
         <f t="shared" si="1"/>
@@ -3173,17 +3165,17 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F42">
         <f t="shared" si="1"/>
@@ -3192,17 +3184,17 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
@@ -3211,17 +3203,17 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
@@ -3230,17 +3222,17 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
@@ -3249,17 +3241,17 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
@@ -3268,17 +3260,17 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
@@ -3287,17 +3279,17 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F48">
         <f t="shared" si="1"/>
@@ -3306,17 +3298,17 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
@@ -3325,17 +3317,17 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
@@ -3344,17 +3336,17 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F51">
         <f t="shared" si="1"/>
@@ -3378,10 +3370,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" t="s">
         <v>385</v>
-      </c>
-      <c r="B1" t="s">
-        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3404,21 +3396,21 @@
         <v>8</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C2">
         <f t="shared" ref="C2:C51" si="0">IF(B2="Common",1,IF(B2="Uncommon",2,IF(B2="Rare",3,IF(B2="Legendary",4,IF(B2="Unique",5,"")))))</f>
@@ -3427,10 +3419,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C3">
         <f t="shared" si="0"/>
@@ -3439,10 +3431,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
@@ -3451,10 +3443,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
@@ -3463,10 +3455,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3475,10 +3467,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3487,10 +3479,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3499,10 +3491,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -3511,10 +3503,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -3526,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -3535,10 +3527,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -3547,10 +3539,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -3559,10 +3551,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -3571,10 +3563,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -3583,10 +3575,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -3595,10 +3587,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -3607,10 +3599,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -3619,10 +3611,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -3631,10 +3623,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -3643,10 +3635,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -3655,10 +3647,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -3667,10 +3659,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -3679,10 +3671,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -3691,10 +3683,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -3703,10 +3695,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -3715,10 +3707,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -3727,10 +3719,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -3739,10 +3731,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -3751,10 +3743,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -3763,10 +3755,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -3775,10 +3767,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -3787,10 +3779,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -3799,10 +3791,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
@@ -3811,10 +3803,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
@@ -3823,10 +3815,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -3835,10 +3827,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
@@ -3847,10 +3839,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -3859,10 +3851,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
@@ -3871,10 +3863,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C40">
         <f t="shared" si="0"/>
@@ -3883,10 +3875,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
@@ -3895,10 +3887,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42">
         <f t="shared" si="0"/>
@@ -3907,10 +3899,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
@@ -3919,10 +3911,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
@@ -3931,25 +3923,25 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C46">
         <f t="shared" si="0"/>
@@ -3958,10 +3950,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B47" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
@@ -3970,10 +3962,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
@@ -3982,47 +3974,47 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4040,32 +4032,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4085,151 +4077,151 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4248,267 +4240,267 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/Survivor Game.xlsx
+++ b/Survivor Game.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtgra\Desktop\GameDev\SurvivorsLike\SurvivorsLike\SurvivorsLikeGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2173BC6-923F-42EB-B62D-3EDD7AF99E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E7AB52-E614-408A-BFA7-02C0C32596F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4142,7 +4142,7 @@
       <c r="A7" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="13" t="s">
         <v>324</v>
       </c>
     </row>
